--- a/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
@@ -575,46 +575,46 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.73733091055925</v>
+        <v>16.68411353733688</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.435269025819323</v>
+        <v>7.411616558924067</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.73811487224634</v>
+        <v>14.69114404416095</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5237623035685743</v>
+        <v>-0.5225115191434782</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-16.46243094076228</v>
+        <v>-16.41068873054846</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.466978469964985</v>
+        <v>-8.440412087815986</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.553849841259712</v>
+        <v>-8.527079605751815</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.024121397049008</v>
+        <v>-8.995440332160136</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.087501487429414</v>
+        <v>-9.058537723833659</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.476793306508974</v>
+        <v>5.459487793417019</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.273042080499842</v>
+        <v>5.256164390917156</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.02211619284031</v>
+        <v>12.98031989186605</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>12.60375366629325</v>
+        <v>12.5633906322967</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.140667947280861</v>
+        <v>5.123909121033442</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-8.048993875763003</v>
+        <v>-8.023562455159983</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.106010195958511</v>
+        <v>-4.093032779780593</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.614525652549865</v>
+        <v>6.593106974667421</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-21.05169389163048</v>
+        <v>-20.98496178116505</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-32.71782056073754</v>
+        <v>-32.61383986338302</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-26.8656941304564</v>
+        <v>-26.78024480879708</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-21.39335678884812</v>
+        <v>-21.32543261133704</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.73658149061074</v>
+        <v>-10.70222056943393</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-16.36688161315496</v>
+        <v>-16.31448070081396</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.6549603871898</v>
+        <v>-11.61775747851755</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.43213638769414</v>
+        <v>-17.37672651306855</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.260422315278937</v>
+        <v>-6.241036743026378</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.25547488324552</v>
+        <v>-12.21685884042487</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-12.00791540285011</v>
+        <v>-11.9701079729751</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.38817516231524</v>
+        <v>-10.35501627824197</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-22.53161361362043</v>
+        <v>-22.45947597835583</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-17.66642004496471</v>
+        <v>-17.61022970067214</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-7.006360618903209</v>
+        <v>-6.984025906627657</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.547096436698624</v>
+        <v>-7.522822943639014</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.981524501767751</v>
+        <v>-1.97503317376767</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.337767812983579</v>
+        <v>-7.314263024699905</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.35222954832437</v>
+        <v>-18.29315214234979</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.870890291879796</v>
+        <v>-7.845235510527168</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.99957783934643</v>
+        <v>-13.95452269146017</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.655878291085358</v>
+        <v>-3.644106866027769</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-30.00917392743824</v>
+        <v>-29.9135125264573</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-14.60192169805521</v>
+        <v>-14.555434666286</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.794808131971642</v>
+        <v>-3.782973470058572</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>18.09479697390501</v>
+        <v>18.03659820502493</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.71966434858998</v>
+        <v>4.704755038641927</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.325814316676336</v>
+        <v>4.311738276240398</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.34393863879756</v>
+        <v>10.31064220238151</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.919298235072773</v>
+        <v>3.906891212047512</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.671565613568362</v>
+        <v>-1.666013834510089</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.647922630755467</v>
+        <v>-7.623210370938246</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.225499450326758</v>
+        <v>-2.217788555408191</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.500829772894527</v>
+        <v>9.470814061989635</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.651223112043468</v>
+        <v>8.623793500758737</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>20.24220397822245</v>
+        <v>20.17718052748698</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>20.28183451223853</v>
+        <v>20.21652083913563</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.165767196138169</v>
+        <v>2.15871303422562</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.417025448447284</v>
+        <v>2.408976994337429</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.125017267577199</v>
+        <v>-5.246127402481385</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.47381795100533</v>
+        <v>-1.510712183332053</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.662376600655548</v>
+        <v>8.871423056197969</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.06200167048549</v>
+        <v>14.39987943953164</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18.79489998230923</v>
+        <v>19.24385660390492</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.557903753474704</v>
+        <v>8.761382839332512</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.204103837257136</v>
+        <v>3.279296558722947</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.736683339582925</v>
+        <v>2.797888094372759</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.313145879398149</v>
+        <v>5.43718252367551</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.100007984463666</v>
+        <v>7.26785432084214</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.896851175448987</v>
+        <v>7.063213535654938</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.572042270803806</v>
+        <v>9.803688644479578</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>11.79224490542688</v>
+        <v>12.07549382323456</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.971479481032709</v>
+        <v>3.04490704203608</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.40366242519201</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>18.97666346316741</v>
+        <v>19.67810580940176</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.89028814966782</v>
+        <v>11.30012942565361</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.023441993924</v>
+        <v>11.43938452434856</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14.33727577594269</v>
+        <v>14.87436514330778</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.6385958711092</v>
+        <v>15.18275057296117</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.001444638317665</v>
+        <v>3.111589854255705</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>14.092780815725</v>
+        <v>14.61012905343687</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.03531561999763</v>
+        <v>14.55321036689507</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.477155044027384</v>
+        <v>5.679571672537278</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.273614806880786</v>
+        <v>5.473694939216287</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.260806595275724</v>
+        <v>-6.486063739106697</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.502617791004042</v>
+        <v>-4.664273749700889</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.26097028574538</v>
+        <v>-4.414552417424602</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.95337019042833</v>
+        <v>5.048719191794838</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.727261781049357</v>
+        <v>9.91423427990356</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.334771367124475</v>
+        <v>9.517676250802296</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.338297541254143</v>
+        <v>7.483610352899412</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.671404523256804</v>
+        <v>4.765120119864406</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.420778483006991</v>
+        <v>-1.445759383852248</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.755653297230019</v>
+        <v>2.808105878817415</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.288244717061673</v>
+        <v>2.330785121115802</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.036166523008099</v>
+        <v>-2.075005998061265</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.376337762018444</v>
+        <v>1.402892046855385</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.227492259809011</v>
+        <v>-5.32464316961179</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.402715851214566</v>
+        <v>2.451633035157059</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.124075145454455</v>
+        <v>4.20529146769141</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.502622518792336</v>
+        <v>6.628925843444968</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.022850084916193</v>
+        <v>-1.034588317429609</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.635065003651142</v>
+        <v>-2.666163547705274</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.854713533642808</v>
+        <v>2.894792541607764</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.901025169329586</v>
+        <v>-2.933125571555188</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.919835706992856</v>
+        <v>3.97263216871746</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.163505221430512</v>
+        <v>7.254730581337121</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.02615016189772</v>
+        <v>10.15229792712777</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9.560621343278889</v>
+        <v>9.680210112082285</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.502010520313085</v>
+        <v>9.621132160161785</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.704418563641234</v>
+        <v>5.776411948106265</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.801579729976055</v>
+        <v>7.900702181509843</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.886331988896018</v>
+        <v>4.950010711990281</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.419506324846147</v>
+        <v>7.514830727911054</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.192038427615472</v>
+        <v>6.272014746754508</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>56</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7077240344956834</v>
+        <v>-0.7062198444232735</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.678428166505505</v>
+        <v>-7.660539209382819</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-11.64865423743807</v>
+        <v>-11.62203019079095</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-9.734208509152239</v>
+        <v>-9.711894074614065</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.337650132341096</v>
+        <v>-1.33533267388799</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.535882038679219</v>
+        <v>2.529345014063622</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.451689647594371</v>
+        <v>2.445430137800365</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.593790462984266</v>
+        <v>-1.5903252909063</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.023690919712443</v>
+        <v>-7.007431466565421</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.087743985719634</v>
+        <v>-6.07364897178384</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.292743511152736</v>
+        <v>-6.278402296100609</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.8883315060710402</v>
+        <v>-0.8868762816131266</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.889405502470701</v>
+        <v>-4.878559463987422</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.849182152047504</v>
+        <v>-2.843123845996033</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.473830477072724</v>
+        <v>-3.50016375060288</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.144805729135129</v>
+        <v>-2.161330507988524</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.540345803538031</v>
+        <v>-2.558203434831562</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.514082764980529</v>
+        <v>1.527015486109661</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>10.79025248261422</v>
+        <v>10.8761957217158</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.127570519364461</v>
+        <v>9.200100579234174</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.153284613765898</v>
+        <v>3.179428926823945</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.703644403600201</v>
+        <v>1.717622898805374</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.625389920623213</v>
+        <v>2.64602929970912</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.571151408466491</v>
+        <v>-3.598401447030916</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.792582768914116</v>
+        <v>-2.813055761448403</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.724439953431919</v>
+        <v>-4.758870623904954</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.141264084412775</v>
+        <v>-5.179125234848961</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.92853109729829</v>
+        <v>-2.949205882771132</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.897539123398708</v>
+        <v>3.9191891699219</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.542861739863596</v>
+        <v>4.567994849823883</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.415259888623289</v>
+        <v>9.468900485554599</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.043320964303952</v>
+        <v>8.08952634812163</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.001659915288101</v>
+        <v>6.038910791889109</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4751954371380549</v>
+        <v>-0.4749035416767029</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9458964528851652</v>
+        <v>0.9530244529172265</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.477818807419915</v>
+        <v>0.4813744990066056</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.33845475237765</v>
+        <v>2.352233789001666</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.247413620200703</v>
+        <v>2.259684361549155</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2169581668110254</v>
+        <v>-0.2177962354951859</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1831778708622878</v>
+        <v>-0.1834130781495773</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.354227190451631</v>
+        <v>-1.361243446670933</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.859671311946023</v>
+        <v>-1.869097871969885</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2843394575679241</v>
+        <v>0.2979019978317297</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-7.440506980399405</v>
+        <v>-7.69096762442377</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-9.758273439654118</v>
+        <v>-10.0740134164319</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-8.773677296483598</v>
+        <v>-9.055944287096885</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-6.787395542838574</v>
+        <v>-6.98868255002165</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.521087727526286</v>
+        <v>-4.657518812376722</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.077290334645362</v>
+        <v>-7.306380660725111</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.109325284070692</v>
+        <v>-6.311949187930061</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.280836603772521</v>
+        <v>-7.522374361468557</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.873765029687569</v>
+        <v>-6.07364897178384</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.40579468601895</v>
+        <v>-4.554264365067063</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.930841156057141</v>
+        <v>-5.094593851399665</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.557278062935232</v>
+        <v>-7.81369903705734</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-7.873479107901986</v>
+        <v>-8.138690348459214</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.038892865664621</v>
+        <v>-7.070424082794133</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.312367280689067</v>
+        <v>-4.33332243545734</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.615924525068159</v>
+        <v>-5.641433151186348</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.850112498713315</v>
+        <v>-6.881043032277375</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.752035953652587</v>
+        <v>-8.789327261048172</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.909273594251744</v>
+        <v>-8.948506327898826</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-8.537718247976109</v>
+        <v>-8.57661904060479</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.729357774872653</v>
+        <v>-6.760697416555246</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.69904619883787</v>
+        <v>-7.734939311870171</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.726563481293198</v>
+        <v>-6.758580478633156</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.567278070666219</v>
+        <v>-5.593470789252102</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-7.80602455735626</v>
+        <v>-7.842192654737723</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.496055718101182</v>
+        <v>-5.522721238285257</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.338584714428137</v>
+        <v>-4.359757896876552</v>
       </c>
     </row>
     <row r="19">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.09913</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.02204801098182685</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.09284</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4081</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.07526538420606954</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.08655</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4063~4076</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4063</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.04005264798230712</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.08027</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4044</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.008410336432859822</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.07398</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4027~4040</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4027</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.06769574595254824</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.06769</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3990~4002</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3990</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.01967520176920345</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.0614</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3965~3976</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3965</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.02864958781561455</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.05511</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3919~3929</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3919</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.08824615935480296</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.04882</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3852~3861</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3852</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.07178589855755746</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.04254</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3796~3805</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3796</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.06242649366595998</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03625</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3695~3703</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3695</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.03154142594178921</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02996</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3563~3570</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3563</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.02367</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3389~3390</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3389</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.1335563143102689</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.01738</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3170~3170</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3170</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3456783990329342</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.01109</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2929~2929</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2929</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.7670601434294966</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.004804</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2626~2626</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2626</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.086150407893605</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.001484</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2238~2238</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2238</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.153567935375364</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.007773</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1925~1925</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1925</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.623444796673141</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.01406</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1618~1618</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1618</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.450937452348739</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.02035</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1313~1313</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1313</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.038168686644553</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.02664</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1013~1013</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1013</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.689187543560998</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.03293</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>810~810</t>
-        </is>
+      <c r="B27" t="n">
+        <v>810</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.802857976086322</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.03922</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>662~662</t>
-        </is>
+      <c r="B28" t="n">
+        <v>662</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>4.606259564986402</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.0455</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>529~529</t>
-        </is>
+      <c r="B29" t="n">
+        <v>529</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.461193059752219</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.05179</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>414~414</t>
-        </is>
+      <c r="B30" t="n">
+        <v>414</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.786754916504997</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.05808</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>324~324</t>
-        </is>
+      <c r="B31" t="n">
+        <v>324</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>4.91396908719743</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.06437</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>244~244</t>
-        </is>
+      <c r="B32" t="n">
+        <v>244</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.654102663396586</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.07066</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>160~160</t>
-        </is>
+      <c r="B33" t="n">
+        <v>160</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.756561679790025</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.07695</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>118~118</t>
-        </is>
+      <c r="B34" t="n">
+        <v>118</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.04893456114596262</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.08323</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.09913</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.09284</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>97~97</t>
-        </is>
+      <c r="B7" t="n">
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3.176664772573531</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.08655</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>115~115</t>
-        </is>
+      <c r="B8" t="n">
+        <v>115</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.419605158050892</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.08027</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>134~134</t>
-        </is>
+      <c r="B9" t="n">
+        <v>134</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2546323500607244</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.07398</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>151~151</t>
-        </is>
+      <c r="B10" t="n">
+        <v>151</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.811197441379427</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.06769</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>188~189</t>
-        </is>
+      <c r="B11" t="n">
+        <v>188</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.4166145898429292</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.0614</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>213~215</t>
-        </is>
+      <c r="B12" t="n">
+        <v>213</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.5298174937435078</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.05511</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>259~262</t>
-        </is>
+      <c r="B13" t="n">
+        <v>259</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.323355572919795</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.04882</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>326~330</t>
-        </is>
+      <c r="B14" t="n">
+        <v>326</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.8398950131233605</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.04254</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>382~386</t>
-        </is>
+      <c r="B15" t="n">
+        <v>382</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.615369969945462</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03625</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>483~488</t>
-        </is>
+      <c r="B16" t="n">
+        <v>483</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.2393399595542292</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02996</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>615~621</t>
-        </is>
+      <c r="B17" t="n">
+        <v>615</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6466582981475142</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.02367</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>789~801</t>
-        </is>
+      <c r="B18" t="n">
+        <v>789</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.5652383339722959</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.01738</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1008~1021</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1008</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.073262022462664</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.01109</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1249~1262</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1249</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.780284595962748</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.004804</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1552~1565</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1552</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.822511802638083</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.001484</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1940~1953</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1940</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-2.467836681705109</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.007773</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2253~2266</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2253</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-2.228654560280589</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.01406</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2560~2573</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2560</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.541242439914605</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.02035</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2865~2878</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2865</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.9298524967214448</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.02664</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3165~3178</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3165</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.8571891068682547</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.03293</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3368~3381</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3368</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.9110662409434838</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.03922</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3516~3529</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3516</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.864081561921509</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.0455</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3649~3662</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3649</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.4999921159500147</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.05179</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3764~3777</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3764</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4150692442237442</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.05808</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3854~3867</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3854</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4117212268559598</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.06437</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3934~3947</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3934</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2258933493460304</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.07066</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4018~4031</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4018</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1491068888033737</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.07695</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4060~4073</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4060</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.00141769659102664</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.08323</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.00230066201549306</v>

--- a/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-9-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-9-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.09599</t>
+          <t>X ≈ -0.09598</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.68411353733688</v>
+        <v>16.69660827357318</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.411616558924067</v>
+        <v>7.424493096899702</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.69114404416095</v>
+        <v>14.70412524934068</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5225115191434782</v>
+        <v>-0.5095649019476198</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-16.41068873054846</v>
+        <v>-16.39761602599098</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.440412087815986</v>
+        <v>-8.427399174829951</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.527079605751815</v>
+        <v>-8.514039651551002</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.995440332160136</v>
+        <v>-8.982282306086354</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.058537723833659</v>
+        <v>-9.045358198717047</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.459487793417019</v>
+        <v>5.472880825920193</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.256164390917156</v>
+        <v>5.269612560097286</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.98031989186605</v>
+        <v>12.99376704899668</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>12.5633906322967</v>
+        <v>12.57694405730616</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.123909121033442</v>
+        <v>5.113479485338786</v>
       </c>
     </row>
     <row r="7">
@@ -624,309 +624,309 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-8.023562455159983</v>
+        <v>-5.096430118338532</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.093032779780593</v>
+        <v>-1.456332348442977</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.593106974667421</v>
+        <v>8.647335430008717</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-20.98496178116505</v>
+        <v>-17.47185796479745</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-32.61383986338302</v>
+        <v>-28.51623907802064</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-26.78024480879708</v>
+        <v>-22.97352827610005</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-21.32543261133704</v>
+        <v>-17.80965213526687</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.70222056943393</v>
+        <v>-7.769394452661267</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-16.31448070081396</v>
+        <v>-13.08887758178131</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.61775747851755</v>
+        <v>-8.683265049111391</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.37672651306855</v>
+        <v>-19.40855282942859</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.241036743026378</v>
+        <v>-8.857875405714196</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.21685884042487</v>
+        <v>-9.280049074295505</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.9701079729751</v>
+        <v>-9.056561000488777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.08341</t>
+          <t>X ≈ -0.08339</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.35501627824197</v>
+        <v>-13.54865121309615</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-22.45947597835583</v>
+        <v>-26.23658146611156</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-17.61022970067214</v>
+        <v>-21.09655689043849</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.984025906627657</v>
+        <v>-9.887877363476271</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.522822943639014</v>
+        <v>-10.42725609744127</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.97503317376767</v>
+        <v>-4.58842436300705</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.314263024699905</v>
+        <v>-10.22016765557293</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.29315214234979</v>
+        <v>-21.78358929623061</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.845235510527168</v>
+        <v>-10.75243631672585</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.95452269146017</v>
+        <v>-17.15434209674031</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.644106866027769</v>
+        <v>-0.7088406139101124</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-29.9135125264573</v>
+        <v>-28.43879807492423</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-14.555434666286</v>
+        <v>-17.75746490276905</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.782973470058572</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.07712</t>
+          <t>X ≈ -0.07711</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>18.03659820502493</v>
+        <v>18.04909327533509</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.704755038641927</v>
+        <v>4.717628579061909</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.311738276240398</v>
+        <v>4.324711794600965</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.31064220238151</v>
+        <v>10.32359448519725</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.906891212047512</v>
+        <v>3.919973914082085</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.666013834510089</v>
+        <v>-1.652998518877958</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.623210370938246</v>
+        <v>-7.61017084530944</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.217788555408191</v>
+        <v>-2.204628744412162</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.470814061989635</v>
+        <v>9.48399870570519</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.623793500758737</v>
+        <v>8.63718695168194</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>20.17718052748698</v>
+        <v>20.19063119039232</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>20.21652083913563</v>
+        <v>20.22996872601907</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.15871303422562</v>
+        <v>2.172265740827079</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.408976994337429</v>
+        <v>2.398547358639277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.07084</t>
+          <t>X ≈ -0.07082</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.246127402481385</v>
+        <v>-5.096113133078759</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.510712183332053</v>
+        <v>-1.455944954658044</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.871423056197969</v>
+        <v>8.646996403718077</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.39987943953164</v>
+        <v>14.02912429496683</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>19.24385660390492</v>
+        <v>18.74709161355094</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.761382839332512</v>
+        <v>8.543322709681235</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.279296558722947</v>
+        <v>3.206948121578051</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.797888094372759</v>
+        <v>2.741542540509201</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.43718252367551</v>
+        <v>5.309504009534677</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.26785432084214</v>
+        <v>7.090633265183691</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.063213535654938</v>
+        <v>6.8877329381612</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.803688644479578</v>
+        <v>9.554066933659747</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>12.07549382323456</v>
+        <v>11.76737664507304</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.04490704203608</v>
+        <v>4.101333736350931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.06455</t>
+          <t>X ≈ -0.06454</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>25</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.40366242519201</v>
+        <v>1.416310031563263</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>19.67810580940176</v>
+        <v>19.68658951649644</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.30012942565361</v>
+        <v>11.3107638747529</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.43938452434856</v>
+        <v>11.44994952149658</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14.87436514330778</v>
+        <v>14.88421842420637</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.18275057296117</v>
+        <v>15.19248722998151</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.111589854255705</v>
+        <v>3.12440738170956</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>14.61012905343687</v>
+        <v>14.62020499413824</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.55321036689507</v>
+        <v>14.56330292190623</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.679571672537278</v>
+        <v>5.692102417197056</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.473694939216287</v>
+        <v>5.486298398034457</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.486063739106697</v>
+        <v>-6.470466720376983</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.664273749700889</v>
+        <v>-6.910802895030642</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.414552417424602</v>
+        <v>-4.424982053122754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.05826</t>
+          <t>X ≈ -0.05825</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>46</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.048719191794838</v>
+        <v>5.060198586834971</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.91423427990356</v>
+        <v>9.924870255232307</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.517676250802296</v>
+        <v>9.528468688934218</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.483610352899412</v>
+        <v>7.494886729599472</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.765120119864406</v>
+        <v>4.777233946202124</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.445759383852248</v>
+        <v>-1.432100744529379</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.808105878817415</v>
+        <v>2.820741902269297</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.330785121115802</v>
+        <v>2.343676619419931</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.075005998061265</v>
+        <v>-2.060988360044881</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.402892046855385</v>
+        <v>1.416236327190177</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.32464316961179</v>
+        <v>-5.309562262935891</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.451633035157059</v>
+        <v>1.246027681745225</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.20529146769141</v>
+        <v>4.218847514043013</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.628925843444968</v>
+        <v>6.618496207746816</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>67</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.034588317429609</v>
+        <v>-1.021657006848656</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.666163547705274</v>
+        <v>-2.652431932053005</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.894792541607764</v>
+        <v>2.907139379415099</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.933125571555188</v>
+        <v>-2.919295798049546</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.97263216871746</v>
+        <v>3.984825389308774</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.254730581337121</v>
+        <v>7.266055662336655</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.15229792712777</v>
+        <v>10.16292001038725</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9.680210112082285</v>
+        <v>9.691089038563256</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.621132160161785</v>
+        <v>9.632041838735205</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.776411948106265</v>
+        <v>5.788520254957277</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.900702181509843</v>
+        <v>7.075749484358802</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.950010711990281</v>
+        <v>4.963463000710391</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.514830727911054</v>
+        <v>7.528386774262657</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.272014746754508</v>
+        <v>6.261585111056355</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>56</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7062198444232735</v>
+        <v>-0.6935665256142087</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.660539209382819</v>
+        <v>-7.645679514230999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-11.62203019079095</v>
+        <v>-11.60610053261637</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-9.711894074614065</v>
+        <v>-9.696465904141121</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.33533267388799</v>
+        <v>-1.321987094260912</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.529345014063622</v>
+        <v>2.541643982308116</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.445430137800365</v>
+        <v>2.457786745238479</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.5903252909063</v>
+        <v>-1.576770839974749</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.007431466565421</v>
+        <v>-6.992434598105561</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.058681967963665</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.278402296100609</v>
+        <v>-6.264945002390391</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.8868762816131266</v>
+        <v>-0.8734239928930165</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.878559463987422</v>
+        <v>-4.865003417635819</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
     <row r="15">
@@ -1043,98 +1043,98 @@
         <v>101</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.50016375060288</v>
+        <v>-3.486610755364353</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.161330507988524</v>
+        <v>-2.147728371798635</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.558203434831562</v>
+        <v>-2.544452556166888</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.527015486109661</v>
+        <v>1.53965623829594</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>10.8761957217158</v>
+        <v>10.88639669512073</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.200100579234174</v>
+        <v>9.210709641201355</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.179428926823945</v>
+        <v>3.191702390444433</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.717622898805374</v>
+        <v>1.730445872060415</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.64602929970912</v>
+        <v>2.658638896663845</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.598401447030916</v>
+        <v>-4.13962908052067</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.813055761448403</v>
+        <v>-2.799598467738186</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.758870623904954</v>
+        <v>-4.745418335184844</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.179125234848961</v>
+        <v>-5.165569188497358</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.949205882771132</v>
+        <v>-2.959635518469284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.0331</t>
+          <t>X ≈ -0.03309</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>132</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.9191891699219</v>
+        <v>3.930698207404937</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.567994849823883</v>
+        <v>4.579722394718118</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.468900485554599</v>
+        <v>9.479295121631047</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.08952634812163</v>
+        <v>8.100270304341194</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.038910791889109</v>
+        <v>6.050240860581617</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4749035416767029</v>
+        <v>-0.4617769719064597</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9530244529172265</v>
+        <v>0.9658347417928042</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4813744990066056</v>
+        <v>0.4944848680955474</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.352233789001666</v>
+        <v>1.948109951542826</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.259684361549155</v>
+        <v>2.273089489201986</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2177962354951859</v>
+        <v>-0.2043389417849681</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1834130781495773</v>
+        <v>-0.1699607894294672</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.361243446670933</v>
+        <v>-1.34768740031933</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.869097871969885</v>
+        <v>-1.879527507668037</v>
       </c>
     </row>
     <row r="17">
@@ -1147,98 +1147,98 @@
         <v>174</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2979019978317297</v>
+        <v>0.3108001229312194</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-7.69096762442377</v>
+        <v>-7.675305316379614</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-10.0740134164319</v>
+        <v>-10.37071360007539</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.055944287096885</v>
+        <v>-9.352041643461945</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-6.98868255002165</v>
+        <v>-7.285626509645567</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.657518812376722</v>
+        <v>-4.955026772038842</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.306380660725111</v>
+        <v>-7.605328849223348</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.311949187930061</v>
+        <v>-6.614666626717167</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.522374361468557</v>
+        <v>-7.509175622513794</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.554264365067063</v>
+        <v>-4.540807071356845</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.094593851399665</v>
+        <v>-5.081141562679555</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.81369903705734</v>
+        <v>-7.800142990705737</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.138690348459214</v>
+        <v>-8.149119984157366</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.02053</t>
+          <t>X ≈ -0.02052</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>219</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.070424082794133</v>
+        <v>-7.296847000103448</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.33332243545734</v>
+        <v>-4.568658204470012</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.641433151186348</v>
+        <v>-5.628426019768746</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.881043032277375</v>
+        <v>-6.868063889878911</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.789327261048172</v>
+        <v>-8.776216456673232</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.948506327898826</v>
+        <v>-8.935463431604461</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-8.57661904060479</v>
+        <v>-8.563552786304314</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.760697416555246</v>
+        <v>-6.747516407260008</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.734939311870171</v>
+        <v>-7.721740572915408</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.758580478633156</v>
+        <v>-6.745175350980325</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.593470789252102</v>
+        <v>-5.580013495541884</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-7.842192654737723</v>
+        <v>-7.828740366017612</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.522721238285257</v>
+        <v>-5.509165191933654</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.359757896876552</v>
+        <v>-4.370187532574704</v>
       </c>
     </row>
     <row r="19">
@@ -1248,205 +1248,205 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.775595996558422</v>
+        <v>-4.332767882386015</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.897543053506183</v>
+        <v>-3.886340806725748</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.782038316119461</v>
+        <v>-6.750247993949927</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.502407590150973</v>
+        <v>-2.504796512913096</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9661400085425456</v>
+        <v>-1.396995531029276</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9910529665175147</v>
+        <v>0.5464690335852396</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.413182825443556</v>
+        <v>-2.830422395639786</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.295303983561261</v>
+        <v>-3.709013673171377</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.356303869743371</v>
+        <v>-3.769995829694054</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.546678017426991</v>
+        <v>-2.973824091044683</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.921555823072467</v>
+        <v>-2.355479981815073</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.187516130953469</v>
+        <v>-0.263488660735554</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2327384799913474</v>
+        <v>-0.6836395140487852</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.642768185059452</v>
+        <v>-2.103994398801959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.007947</t>
+          <t>X ≈ -0.007945</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.998388815259482</v>
+        <v>-2.149790202719856</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.959797411722086</v>
+        <v>-1.774221328896196</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.684699121618934</v>
+        <v>-2.500118541465802</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.214511995612249</v>
+        <v>-3.363270881321142</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.75293321068434</v>
+        <v>-3.570434606602277</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-6.425788302671648</v>
+        <v>-6.253193027298309</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.530324000141945</v>
+        <v>-4.35114841967706</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.337441392322717</v>
+        <v>-4.155965407834657</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.748276262003436</v>
+        <v>-2.56131842528459</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.278269433830047</v>
+        <v>-2.086733910356095</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.473121768048543</v>
+        <v>-3.284812552060004</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.768771614003434</v>
+        <v>-3.58156022751924</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.548762198545774</v>
+        <v>-1.352704458316246</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.638974859668906</v>
+        <v>-0.4647171524604303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.00166</t>
+          <t>X ≈ -0.001656</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.070757907838782</v>
+        <v>-5.19409432510794</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.620475850700068</v>
+        <v>-4.738096955639584</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.953488887193508</v>
+        <v>-3.065684877862267</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.946947094792193</v>
+        <v>-6.811428726522024</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.454440474812813</v>
+        <v>-6.316126548351505</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.86833874328272</v>
+        <v>-4.726762854633733</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.757196171895259</v>
+        <v>-6.620258743615722</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.4202558593365</v>
+        <v>-5.278541857686641</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.54311141562183</v>
+        <v>-7.406707476741659</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-8.650968559412711</v>
+        <v>-8.515024205888118</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-9.113453842493172</v>
+        <v>-8.978123296964903</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.532678932570363</v>
+        <v>-7.393357547710238</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-7.179737667226661</v>
+        <v>-7.03831460257409</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.672284376187434</v>
+        <v>-6.554181019530965</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.004629</t>
+          <t>X ≈ 0.004632</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>313</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7362498218074904</v>
+        <v>-0.7237275321318677</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.347823434771605</v>
+        <v>-2.334913625195554</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.784225687694146</v>
+        <v>-1.771218556276544</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3760172835210795</v>
+        <v>-0.3630381411226153</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.233927316484696</v>
+        <v>-1.220816512109757</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3414698927965318</v>
+        <v>0.3545127890908972</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.06275264236711564</v>
+        <v>-0.04968638806663961</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4285304125254328</v>
+        <v>0.4417114218206706</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.006508162125876</v>
+        <v>1.019706901080639</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.802083476576172</v>
+        <v>-0.7886783489233409</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9100961064544251</v>
+        <v>0.9235534001646428</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.6249904459084803</v>
+        <v>0.6384427346285904</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7537306187104704</v>
+        <v>-0.7401745723588675</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.142986922217084</v>
+        <v>-1.153416557915236</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>307</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.532620311711852</v>
+        <v>3.545142601387475</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.549711193861604</v>
+        <v>3.562621003437656</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.132041184333417</v>
+        <v>4.145048315751019</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.58802721596372</v>
+        <v>4.601006358362184</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1849216864049126</v>
+        <v>-0.1718108820299733</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.190411344780529</v>
+        <v>-1.177368448486163</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.6236792640070945</v>
+        <v>-0.6106130097066185</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.719527157902597</v>
+        <v>-2.706346148607359</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.151862548970975</v>
+        <v>-1.138663810016212</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.676254834976064</v>
+        <v>-1.662849707323232</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5780765632023304</v>
+        <v>-0.5646192694921126</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.823823699016572</v>
+        <v>-2.810371410296462</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.592612511915874</v>
+        <v>-2.579056465564271</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.645822775730714</v>
+        <v>-3.656252411428866</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>305</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.227873155199866</v>
+        <v>4.240395444875489</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.206463476661838</v>
+        <v>7.219373286237889</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.860775097934095</v>
+        <v>3.873782229351697</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.023815115787492</v>
+        <v>2.036794258185957</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.124738163010491</v>
+        <v>3.13784896738543</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.405786658103153</v>
+        <v>4.418829554397519</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.632528350666909</v>
+        <v>5.645594604967386</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.14895150926246</v>
+        <v>6.162132518557698</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.448607360785076</v>
+        <v>4.461806099739839</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.237826438052267</v>
+        <v>5.251231565705098</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.065859998980585</v>
+        <v>3.079317292690803</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.428112008785</v>
+        <v>3.44156429750511</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.040644283086003</v>
+        <v>1.054200329437606</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.29036561536229</v>
+        <v>1.279935979664138</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>300</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1601049868765969</v>
+        <v>-0.1475826972009742</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.771678599840932</v>
+        <v>-1.758768790264881</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.833213973104151</v>
+        <v>-3.820206841686549</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.369627507163322</v>
+        <v>-5.356648364764858</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.24138205556882</v>
+        <v>-3.228271251193881</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.695340501792074</v>
+        <v>-3.682274247491598</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.495857233906946</v>
+        <v>-2.482676224611708</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.223523786755955</v>
+        <v>-2.210325047801192</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7403156384505039</v>
+        <v>-0.7269105107976728</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.61173562943479</v>
+        <v>-1.598278335724572</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.577352472089323</v>
+        <v>-2.563900183369213</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.664273749700932</v>
+        <v>-4.650717703349329</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.414552417424602</v>
+        <v>-3.424982053122754</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>203</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.754522064052388</v>
+        <v>-1.741999774376765</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.366095677016538</v>
+        <v>-3.353185867440487</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.790521033859491</v>
+        <v>-1.777513902441889</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.29539712337855</v>
+        <v>1.308376265777014</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.74219758318317</v>
+        <v>1.755308387558109</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.502693708091037</v>
+        <v>4.515736604385403</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.40318166569552</v>
+        <v>5.416247919995996</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.860220055608679</v>
+        <v>5.873418794563442</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.517484033142274</v>
+        <v>4.530889160795105</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.820119871386268</v>
+        <v>3.833577165096486</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.884059678977941</v>
+        <v>1.897511967698051</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.941637580348434</v>
+        <v>2.955193626700037</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.713526400309441</v>
+        <v>1.703096764611288</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>148</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2092643824927194</v>
+        <v>0.2217866721683421</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.0509578791201406</v>
+        <v>-0.03804806954408946</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.932551792661613</v>
+        <v>2.945558924079215</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3155734531092662</v>
+        <v>-0.302594310710802</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.848708034521266</v>
+        <v>1.861818838896205</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.173176999263916</v>
+        <v>4.186219895558281</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.115470309018654</v>
+        <v>6.12853656331913</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.999638261588551</v>
+        <v>7.012819270883789</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.262962699730579</v>
+        <v>6.276161438685342</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.439864541729669</v>
+        <v>7.4532696693825</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.883759866060743</v>
+        <v>5.89721715977096</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.242467347730567</v>
+        <v>5.255919636450678</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.470861385434283</v>
+        <v>3.484417431785886</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.071934069061768</v>
+        <v>5.061504433363616</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>133</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.160697018135885</v>
+        <v>9.173219307811507</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>12.06040160066028</v>
+        <v>12.07331141023633</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.658014097071238</v>
+        <v>8.67102122848884</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.021349936445702</v>
+        <v>2.034329078844166</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.986688119869818</v>
+        <v>2.999798924244757</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.227148137903242</v>
+        <v>-1.214105241608877</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.447516641065071</v>
+        <v>2.460582895365548</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.4765738437872855</v>
+        <v>0.4897548530825233</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.821087870321378</v>
+        <v>1.834492997974209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.120093944500084</v>
+        <v>3.133551238210302</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.665755297334243</v>
+        <v>7.679207586054353</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>13.26053828037426</v>
+        <v>13.27409432672586</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.00650021415439</v>
+        <v>11.99607057845623</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>115</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.289170375442197</v>
+        <v>2.30169266511782</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.155857632043187</v>
+        <v>4.168767441619238</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2827280558813996</v>
+        <v>0.2957351872990017</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.630372492836734</v>
+        <v>5.643351635235199</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.483255625590544</v>
+        <v>2.496366429965484</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.258958432871424</v>
+        <v>6.272001329165789</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.913355150381832</v>
+        <v>7.926421404682308</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.315736968991565</v>
+        <v>8.328917978286803</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.254737082809307</v>
+        <v>8.26793582176407</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.88287276734664</v>
+        <v>10.89627789499947</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.54768466042032</v>
+        <v>11.56114195413053</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.32119825254831</v>
+        <v>13.33465054126842</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.37920451116872</v>
+        <v>16.39276055752032</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.49849106083626</v>
+        <v>17.48806142513811</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>90</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2712160979877467</v>
+        <v>-0.258693808312124</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.783876955714689</v>
+        <v>4.79678676529074</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9.944563804673621</v>
+        <v>9.957570936091223</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>18.96370582616995</v>
+        <v>18.97668496856841</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.98084016665339</v>
+        <v>13.99395097102833</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>16.50050432659128</v>
+        <v>16.51354722288565</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.19354838709678</v>
+        <v>14.20661464139725</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>14.83747609942645</v>
+        <v>14.85065710872168</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.220920657688559</v>
+        <v>9.234119396643322</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.259684361549489</v>
+        <v>7.27308948920232</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.05493103723191</v>
+        <v>7.068388330942128</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.31153641679964</v>
+        <v>9.32498870551975</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.11350402807683</v>
+        <v>11.12706007442843</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.5854475825754</v>
+        <v>13.57501794687725</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>80</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.756561679790032</v>
+        <v>8.769083969465655</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.89498806682577</v>
+        <v>10.90789787640182</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.00011936022918</v>
+        <v>18.01312649164678</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.63037249283668</v>
+        <v>15.64335163523514</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21.34195127776451</v>
+        <v>21.35506208213945</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>17.88939321548017</v>
+        <v>17.90243611177453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.55465949820786</v>
+        <v>16.56772575250834</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.58747609942636</v>
+        <v>13.6006571087216</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.52647621324406</v>
+        <v>13.53967495219882</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>15.17635102821616</v>
+        <v>15.18975615586899</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.47159770389858</v>
+        <v>12.4850549976088</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.25598086124401</v>
+        <v>11.26943314996412</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.33572625029911</v>
+        <v>13.34928229665071</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.5854475825754</v>
+        <v>13.57501794687725</v>
       </c>
     </row>
     <row r="32">
@@ -1927,150 +1927,150 @@
         <v>84</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.471464921846604</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.833452693562492</v>
+        <v>3.846459824980094</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.535134397598597</v>
+        <v>7.548113539997061</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.209421402969774</v>
+        <v>7.22248765727025</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.12319038514071</v>
+        <v>9.136371394435947</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.490761927529789</v>
+        <v>5.503960666484552</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.59301769488285</v>
+        <v>10.60642282253568</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.80359990886306</v>
+        <v>12.81705219758317</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.57382148839434</v>
+        <v>13.58737753474594</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07381</t>
+          <t>X ≈ 0.07379</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>42</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689588</v>
+        <v>12.17979315831348</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12.29703915950331</v>
+        <v>12.31001830190177</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.209421402969831</v>
+        <v>7.222487657270307</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.20504764181553</v>
+        <v>16.2182463807703</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.59301769488279</v>
+        <v>10.60642282253562</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.80359990886306</v>
+        <v>12.81705219758317</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.38334529791816</v>
+        <v>12.39690134426976</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08009</t>
+          <t>X ≈ 0.08008</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>34</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.79025081757829</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.20600171317035</v>
+        <v>10.21900884458795</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.10096072813079</v>
+        <v>22.11393987052926</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.68018657188216</v>
+        <v>15.6932973762571</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.66943031393162</v>
+        <v>-1.656387417637255</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.069365380560853</v>
+        <v>7.082431634861329</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.42571139354401</v>
+        <v>15.43889240283925</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>18.30588797794999</v>
+        <v>18.31908671690475</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.45576279292204</v>
+        <v>17.46916792057488</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.25100946860447</v>
+        <v>17.26446676231468</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.461863214185186</v>
+        <v>8.475315502905296</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.98278507382854</v>
+        <v>10.99634112018015</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.2913299355166</v>
+        <v>8.280900299818448</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-9-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-9-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,417 +2210,417 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.09913</t>
+          <t>X &gt; -0.09912</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02204801098182685</v>
+        <v>-0.02229869849929855</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.01343862581914124</v>
+        <v>-0.01369939654680508</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05408283221905918</v>
+        <v>-0.05433575871854401</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1298614252919776</v>
+        <v>-0.1300953805992009</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1676148933298123</v>
+        <v>-0.1678424012913524</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1006116601902391</v>
+        <v>-0.1008541636337057</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1232849055960656</v>
+        <v>-0.1235224191152255</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.008207806743463664</v>
+        <v>0.007935821230766749</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03385606198768443</v>
+        <v>0.03357739122324688</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.02688787545871207</v>
+        <v>0.02660660719858754</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.04213185431474642</v>
+        <v>-0.04239741820379095</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1405035137559878</v>
+        <v>-0.1407450291913577</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1074971929243347</v>
+        <v>-0.1077489533492866</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1370731795154683</v>
+        <v>-0.136825764966467</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.09284</t>
+          <t>X &gt; -0.09283</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07526538420606954</v>
+        <v>-0.07554362516194146</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03709109271491684</v>
+        <v>-0.03738790767243216</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1010536602986889</v>
+        <v>-0.1013372268970727</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1286106408714645</v>
+        <v>-0.1288868789388573</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1158726831156898</v>
+        <v>-0.1161552241426307</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.07404527803902283</v>
+        <v>-0.07433650436238537</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0965146700895616</v>
+        <v>-0.09680102665524259</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.03688887163093568</v>
+        <v>0.03656708915215034</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.06281982557888455</v>
+        <v>0.06249119883452181</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.009582362365492259</v>
+        <v>0.00926178484598239</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.05900954389769453</v>
+        <v>-0.05931464743404291</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1822998147295394</v>
+        <v>-0.1825746854913106</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1478602269179419</v>
+        <v>-0.1481460648481914</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1538320057607905</v>
+        <v>-0.1535464823241242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.08655</t>
+          <t>X &gt; -0.08654</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>4063</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.04005264798230712</v>
+        <v>-0.05206421502895608</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.01912236262208467</v>
+        <v>-0.0307524303466451</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1307102912190317</v>
+        <v>-0.1422490606359901</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.03621233407223201</v>
+        <v>-0.04778511900006777</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.02810059014171884</v>
+        <v>0.01665343773865402</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.04426916733474684</v>
+        <v>0.03274807443727212</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.002465808917413881</v>
+        <v>-0.01396957918696273</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.08446553171933857</v>
+        <v>0.07307047809985079</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1353749349746636</v>
+        <v>0.1239915697013032</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.06109408206420852</v>
+        <v>0.04991106120461808</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.01771182096695867</v>
+        <v>0.03116911467717642</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1554582531471382</v>
+        <v>-0.1420059644270282</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.09439185993710453</v>
+        <v>-0.1054421127981087</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1014832567059258</v>
+        <v>-0.111912892404078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.08027</t>
+          <t>X &gt; -0.08025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.008410336432859822</v>
+        <v>0.007994762959981472</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.08630956583957783</v>
+        <v>0.08586188921916715</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.04858594186700316</v>
+        <v>-0.04900368586801562</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.003569293053800493</v>
+        <v>-0.003997316676070284</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06357723384642355</v>
+        <v>0.06312818968754641</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05375649287405082</v>
+        <v>0.05331200617374066</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03188734318443665</v>
+        <v>0.0314473714619723</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1708094327597252</v>
+        <v>0.17033126325137</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1728703846444333</v>
+        <v>0.1723910015815733</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1269439135916457</v>
+        <v>0.1264689244538246</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.0349162114350321</v>
+        <v>0.03446211223331375</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01564543633384829</v>
+        <v>-0.01608698840998102</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02644927504081807</v>
+        <v>-0.02689170236065763</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.08418644314171075</v>
+        <v>-0.08382012481620649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.07398</t>
+          <t>X &gt; -0.07397</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.06769574595254824</v>
+        <v>-0.06814691397904227</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06681277591216883</v>
+        <v>0.06631371798597741</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.06699307166780244</v>
+        <v>-0.06746276311925214</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.04711078682643688</v>
+        <v>-0.04758447174851455</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04735266527690385</v>
+        <v>0.04685053891427771</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0610165116387833</v>
+        <v>0.06051341603617999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.06420337525300113</v>
+        <v>0.06369849104616065</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1808929107331139</v>
+        <v>0.1803546793711135</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1336190703869491</v>
+        <v>0.1330917635055755</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.09107442191499615</v>
+        <v>0.09054980666264356</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.05011445491035005</v>
+        <v>-0.05060612866259362</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1010556242362597</v>
+        <v>-0.1015345919713653</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.03567394831062387</v>
+        <v>-0.03617315135127086</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.0947113446657184</v>
+        <v>-0.09429684954778139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.06769</t>
+          <t>X &gt; -0.06768</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3990</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.01967520176920345</v>
+        <v>-0.02026152141618809</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08144145347910126</v>
+        <v>0.08081141963020144</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1498806397708208</v>
+        <v>-0.1504576123272301</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1810803703791279</v>
+        <v>-0.181648364764861</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1306600278883181</v>
+        <v>-0.1312469951298709</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.01966357711427946</v>
+        <v>-0.02027524390329916</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03438922793761634</v>
+        <v>0.03376278027919</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1566250355966048</v>
+        <v>0.1559624140269378</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.08443815615846262</v>
+        <v>0.08379259925767713</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02452282886730472</v>
+        <v>0.02388234515291288</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1160776468028217</v>
+        <v>-0.1166855483466236</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1929041299862533</v>
+        <v>-0.1934927017392809</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1479830228838495</v>
+        <v>-0.1485879113172146</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1238256003819984</v>
+        <v>-0.1342552360801506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.0614</t>
+          <t>X &gt; -0.06139</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3965</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02864958781561455</v>
+        <v>-0.02931934961909377</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.04211885141322114</v>
+        <v>-0.04280634895029323</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2220749024784183</v>
+        <v>-0.2227225649569888</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2543493798036423</v>
+        <v>-0.2549875695962669</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2252692660421403</v>
+        <v>-0.2259220608255674</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1155173863833454</v>
+        <v>-0.1161943011156907</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.01498695412728779</v>
+        <v>0.01427573991708186</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06549323220542647</v>
+        <v>0.06476290217251091</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.006789915788175449</v>
+        <v>-0.007503178312610714</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.0111332168052698</v>
+        <v>-0.0118567473568234</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1513221145582975</v>
+        <v>-0.1520133159782944</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1532246873058014</v>
+        <v>-0.1539153119622512</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.119507040999757</v>
+        <v>-0.1059509946481541</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09677183734893902</v>
+        <v>-0.1072014730470912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.05511</t>
+          <t>X &gt; -0.0551</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3919</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.08824615935480296</v>
+        <v>-0.0890585241730264</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.158983419935943</v>
+        <v>-0.1598038288666999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3363970645225365</v>
+        <v>-0.337179007334889</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3451751383400961</v>
+        <v>-0.3459531775990783</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2838449005794459</v>
+        <v>-0.2846475459807749</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.09990342060545743</v>
+        <v>-0.1007486016012678</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.01779780487648708</v>
+        <v>-0.0186656848004958</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.03890394236366745</v>
+        <v>0.03801372355720645</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01748615968632095</v>
+        <v>0.01659999044463945</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.02773060443690412</v>
+        <v>-0.0286192585660956</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.09059928512923676</v>
+        <v>-0.09147561463609577</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1837996950203404</v>
+        <v>-0.1703474063002304</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1702701773610116</v>
+        <v>-0.1567141310094087</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1757159795578005</v>
+        <v>-0.1861456152559526</v>
       </c>
     </row>
     <row r="14">
@@ -2633,254 +2633,254 @@
         <v>3852</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.07178589855755746</v>
+        <v>-0.07283731484299949</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1153746274747576</v>
+        <v>-0.1164481479441974</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3925989605793205</v>
+        <v>-0.3936092596485565</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3001614625806397</v>
+        <v>-0.3011935837335074</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3578801974753105</v>
+        <v>-0.3589088872747581</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2278267015322868</v>
+        <v>-0.2288835667320726</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1946919933615021</v>
+        <v>-0.1957597246700615</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1287927121978996</v>
+        <v>-0.1298876383600813</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1495554503946366</v>
+        <v>-0.1506467914441103</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1286853165398085</v>
+        <v>-0.12980003411284</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2295964809404651</v>
+        <v>-0.2161391872302474</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2730949435327261</v>
+        <v>-0.2596426548126161</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.303941454789161</v>
+        <v>-0.2903854084375581</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2878649823259494</v>
+        <v>-0.2982946180241015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04254</t>
+          <t>X &gt; -0.04253</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3796</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.06242649366595998</v>
+        <v>-0.0636800872868406</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.004065560934485291</v>
+        <v>-0.005374134110667228</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2269382258870465</v>
+        <v>-0.2281984294888701</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1613160921186036</v>
+        <v>-0.1625910415989367</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3434604559897636</v>
+        <v>-0.344701200343458</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2685015213619408</v>
+        <v>-0.2697554167705931</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2336400543059298</v>
+        <v>-0.2349058264390038</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1072316414898751</v>
+        <v>-0.1085426806966439</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.04838551970297544</v>
+        <v>-0.04971419998651072</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.04098300761102536</v>
+        <v>-0.0423349687030381</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1403622539517926</v>
+        <v>-0.1269049602415748</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2640402135715831</v>
+        <v>-0.2505879248514731</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2364549931150108</v>
+        <v>-0.2228989467634079</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.250168855780764</v>
+        <v>-0.2605984914789161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03625</t>
+          <t>X &gt; -0.03624</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3695</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.03154142594178921</v>
+        <v>0.02988310553476481</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.05490162706347235</v>
+        <v>0.05318548104670384</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.163214873761639</v>
+        <v>-0.1648853938205406</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.207465345001161</v>
+        <v>-0.209120669547346</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6501411796564156</v>
+        <v>-0.6516946746173105</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5273185205933899</v>
+        <v>-0.5288966808721298</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3269336854545415</v>
+        <v>-0.3285695422455603</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.157112645162357</v>
+        <v>-0.1588100267936525</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1220352887856819</v>
+        <v>-0.1237449612210639</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0562563056180494</v>
+        <v>0.06966143327088048</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.06730622032333855</v>
+        <v>-0.0538489266131208</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1411774608128127</v>
+        <v>-0.1277251720927026</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1013508809593517</v>
+        <v>-0.08779483460774884</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1763927421877938</v>
+        <v>-0.1868223778859459</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02996</t>
+          <t>X &gt; -0.02995</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3563</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1146320764598627</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1122968869428007</v>
+        <v>-0.1145110871836152</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.520060011968134</v>
+        <v>-0.522177515077793</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5148475800537042</v>
+        <v>-0.5169622661101556</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.8979533773112109</v>
+        <v>-0.8999841752196787</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5292603609574158</v>
+        <v>-0.5313832937218237</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3743528474711226</v>
+        <v>-0.3765238968605047</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1807669541801218</v>
+        <v>-0.1830129249484074</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2137006040447105</v>
+        <v>-0.2005018650899473</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.02537504531737511</v>
+        <v>-0.01196991766454403</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.06173095172870546</v>
+        <v>-0.04827365801848771</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1396127396541047</v>
+        <v>-0.1261604509339946</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.05467509688023142</v>
+        <v>-0.04111905052862852</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1136823640987572</v>
+        <v>-0.1241119997969093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.02367</t>
+          <t>X &gt; -0.02366</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3389</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1335563143102689</v>
+        <v>-0.136474862737245</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2768116135947238</v>
+        <v>0.2736795873162734</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.02953540518834785</v>
+        <v>-0.01652827377074573</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.07632564820787735</v>
+        <v>-0.06334650580941315</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5852396340088717</v>
+        <v>-0.5721288296339324</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3173049255643861</v>
+        <v>-0.3042620292700207</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.01844466231143116</v>
+        <v>-0.005378408010955127</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1340237536016673</v>
+        <v>0.1472047628969051</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1615455552328768</v>
+        <v>0.17474429418764</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2851589361536071</v>
+        <v>0.2985640638064382</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.168927299649539</v>
+        <v>0.1823845933597568</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1147887691814589</v>
+        <v>0.1282410579015689</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3436932022023313</v>
+        <v>0.3572492485539343</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2983422417669033</v>
+        <v>0.2879126060687511</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>3170</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3456783990329342</v>
+        <v>0.3582006887085569</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5953035242390214</v>
+        <v>0.6082133338150726</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3581635242670345</v>
+        <v>0.3711706556846366</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3937794328997626</v>
+        <v>0.4067585752982268</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.018458816872716</v>
+        <v>-0.005348012497776722</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2789831208429447</v>
+        <v>0.2920260171373101</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5727982994697243</v>
+        <v>0.5858645537702003</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6103467618869587</v>
+        <v>0.6235277711821965</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7070755823292671</v>
+        <v>0.7202743212840303</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7717768957240452</v>
+        <v>0.7851820233768763</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.567023571406466</v>
+        <v>0.5804808651166837</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6644982114017424</v>
+        <v>0.6779505001218524</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7489754616555757</v>
+        <v>0.7625315080071786</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6201478980328048</v>
+        <v>0.6097182623346526</v>
       </c>
     </row>
     <row r="20">
@@ -2942,205 +2942,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7670601434294966</v>
+        <v>0.7476456367017192</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9649778244222134</v>
+        <v>0.981351924915657</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.94566391468463</v>
+        <v>0.9623919511616421</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6320795600951286</v>
+        <v>0.6484763362942445</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.05951699985396175</v>
+        <v>0.1101867831985501</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2203935568936188</v>
+        <v>0.2709021179241731</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8184867430013369</v>
+        <v>0.8694852332053244</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9317062120928341</v>
+        <v>0.983216042783809</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.041413051755526</v>
+        <v>1.093057254897865</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.04482149595259</v>
+        <v>1.097255301752156</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.771785481297016</v>
+        <v>0.8242247960372282</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7037446031354477</v>
+        <v>0.7561089272104553</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8297515148945394</v>
+        <v>0.8825928535348879</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8063420858188195</v>
+        <v>0.8350111139425067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.004804</t>
+          <t>X &gt; -0.0048</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.086150407893605</v>
+        <v>1.080988731370411</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.302451890131174</v>
+        <v>1.298374066878011</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.364551957335038</v>
+        <v>1.360745539265828</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.07591704729213</v>
+        <v>1.110018301901803</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4994151010699142</v>
+        <v>0.5336335107108781</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9872606945357632</v>
+        <v>1.021483730822155</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.435657213364017</v>
+        <v>1.470106704889318</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.539684781833095</v>
+        <v>1.574466632531148</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.478684895650794</v>
+        <v>1.513484476008372</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.428255064773666</v>
+        <v>1.46356567967851</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.261582471606125</v>
+        <v>1.296959759513555</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.219804166651478</v>
+        <v>1.25514743567841</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.104195404906882</v>
+        <v>1.139758487126905</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9731094256827859</v>
+        <v>0.9845417564010575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001484</t>
+          <t>X &gt; 0.001488</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2238</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.153567935375364</v>
+        <v>2.166090225050986</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.329304420713171</v>
+        <v>2.342214230289223</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.113166723946783</v>
+        <v>2.126173855364385</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.466833618842045</v>
+        <v>2.47981276124051</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.704998641482113</v>
+        <v>1.718109445857053</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.002440579197774</v>
+        <v>2.01548347549214</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.856044663534078</v>
+        <v>2.869110917834554</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.746323284412988</v>
+        <v>2.759504293708225</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.042785417891089</v>
+        <v>3.055984156845852</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.175680786929291</v>
+        <v>3.189085914582122</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.06029296752682</v>
+        <v>3.073750261237038</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.737214105211834</v>
+        <v>2.750666393931944</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.540373256554695</v>
+        <v>2.553929302906297</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.29858431179791</v>
+        <v>2.288154676099758</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.007773</t>
+          <t>X &gt; 0.007776</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1925</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.623444796673141</v>
+        <v>2.635967086348764</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.089793261630966</v>
+        <v>3.102703071207017</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.746872606982421</v>
+        <v>2.759879738400024</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.929073791537974</v>
+        <v>2.942052933936438</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.182860368673602</v>
+        <v>2.195971173048541</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.272510098597046</v>
+        <v>2.285552994891411</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.330633524181913</v>
+        <v>3.343699778482389</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.123190385140674</v>
+        <v>3.136371394435912</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.37387881064668</v>
+        <v>3.387077549601443</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.822454924320056</v>
+        <v>3.835860051972887</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.409909392210274</v>
+        <v>3.423366685920492</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.080656185919338</v>
+        <v>3.094108474639448</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.075985990558848</v>
+        <v>3.089542036910451</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.858174855302678</v>
+        <v>2.847745219604526</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1618</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.450937452348739</v>
+        <v>2.463459742024362</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.00252823987892</v>
+        <v>3.015438049454971</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.484050138968364</v>
+        <v>2.497057270385966</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.614303271575864</v>
+        <v>2.627282413974328</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.632124330916554</v>
+        <v>2.645235135291493</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.929566268632215</v>
+        <v>2.94260916492658</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.080926494499607</v>
+        <v>4.093992748800083</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.231790067287946</v>
+        <v>4.244971076583184</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.232594878262631</v>
+        <v>4.245793617217394</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.865782425002322</v>
+        <v>4.879187552655154</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.166591523428863</v>
+        <v>4.180048817139081</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.200974680774294</v>
+        <v>4.214426969494404</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.151548252771299</v>
+        <v>4.165104299122902</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.092246099262667</v>
+        <v>4.081816463564515</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1313</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.038168686644553</v>
+        <v>2.050690976320176</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.025985781981895</v>
+        <v>2.038895591557946</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.164247311485838</v>
+        <v>2.17725444290344</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.751469217893799</v>
+        <v>2.764448360292263</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.517693852021928</v>
+        <v>2.530804656396867</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.586651402837369</v>
+        <v>2.599694299131734</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.720501082366305</v>
+        <v>3.733567336666781</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.786447919685337</v>
+        <v>3.799628928980574</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.18241680730349</v>
+        <v>4.195615546258253</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.779359405977011</v>
+        <v>4.792764533629843</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.422283157059276</v>
+        <v>4.435740450769494</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.380504852104636</v>
+        <v>4.393957140824746</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>4.887743835112254</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.743101809536554</v>
+        <v>4.732672173838402</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1013</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.689187543560998</v>
+        <v>2.70170983323662</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.15066427610514</v>
+        <v>3.163574085681191</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.940395766941911</v>
+        <v>3.953402898359514</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.156532413863331</v>
+        <v>5.169511556261796</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.223244466313368</v>
+        <v>4.236355270688307</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.718119770267926</v>
+        <v>4.731162666562291</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.916702933548457</v>
+        <v>5.929769187848933</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.646952901005854</v>
+        <v>5.660133910301091</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.079536430420795</v>
+        <v>6.092735169375558</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.414011442826229</v>
+        <v>6.42741657047906</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.20925811850865</v>
+        <v>6.222715412218868</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.441074642092978</v>
+        <v>6.454526930813088</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.699003644178681</v>
+        <v>7.712559690530284</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.158991511499387</v>
+        <v>7.148561875801235</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>810</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.802857976086322</v>
+        <v>3.815380265761945</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.783876955714661</v>
+        <v>4.796786765290712</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.376662570105722</v>
+        <v>5.389669701523324</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.124199653330507</v>
+        <v>6.137178795728971</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.845037697517597</v>
+        <v>4.858148501892536</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.772109264862877</v>
+        <v>4.785152161157242</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.045400238948631</v>
+        <v>6.058466493249107</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.565871161154782</v>
+        <v>6.579052170450019</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.134500904602113</v>
+        <v>6.147699643556876</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.889313991179122</v>
+        <v>6.902719118831953</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.808017456984999</v>
+        <v>6.821474750695216</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.583141355071177</v>
+        <v>7.596593643791287</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.891281805854668</v>
+        <v>8.904837852206271</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.523719187513663</v>
+        <v>8.513289551815511</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>662</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.606259564986402</v>
+        <v>4.618781854662025</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.864776586463222</v>
+        <v>5.877686396039273</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.923080085304704</v>
+        <v>5.936087216722306</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.563907236039093</v>
+        <v>7.576886378437557</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.514912002840035</v>
+        <v>5.528022807214974</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.906009529679565</v>
+        <v>4.919052425973931</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.029735026908803</v>
+        <v>6.042801281209279</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.468896039003425</v>
+        <v>6.482077048298663</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.105781349195752</v>
+        <v>6.118980088150515</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.766230182294706</v>
+        <v>6.779635309947537</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.014649063415199</v>
+        <v>7.028106357125417</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.106434033449446</v>
+        <v>8.119886322169556</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.10309785150756</v>
+        <v>10.11665389785917</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.295417371095041</v>
+        <v>9.284987735396889</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>529</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.461193059752219</v>
+        <v>3.473715349427842</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.307086365502521</v>
+        <v>4.319996175078572</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.235469076675308</v>
+        <v>5.24847620809291</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.957404628942541</v>
+        <v>8.970383771341005</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.150552411980001</v>
+        <v>6.163663216354941</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.447994349695662</v>
+        <v>6.461037245990028</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.930368382895978</v>
+        <v>6.943434637196454</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.975472318708057</v>
+        <v>7.988653328003295</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.158328765228958</v>
+        <v>7.171527504183722</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.009526831618814</v>
+        <v>8.022931959271645</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.99380942412543</v>
+        <v>8.007266717835648</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.217228498295057</v>
+        <v>8.230680787015167</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.309261221943721</v>
+        <v>9.322817268295324</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.61380297009903</v>
+        <v>8.603373334400878</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>414</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.786754916504997</v>
+        <v>3.799277206180619</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.349094347019012</v>
+        <v>4.362004156595063</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.611230471340292</v>
+        <v>6.624237602757894</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.881580222305267</v>
+        <v>9.894559364703731</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.169245963754847</v>
+        <v>7.182356768129786</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.500504326591283</v>
+        <v>6.513547222885649</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.6573165030388</v>
+        <v>6.670382757339276</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.880954360295959</v>
+        <v>7.894135369591197</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.853770899234426</v>
+        <v>6.86696963818919</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.211375182805533</v>
+        <v>7.224780310458364</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.006621858487954</v>
+        <v>7.020079152198171</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.799459122113582</v>
+        <v>6.812911410833692</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.345388086047898</v>
+        <v>7.3589441323995</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.145834056005349</v>
+        <v>6.135404420307196</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>324</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.91396908719743</v>
+        <v>4.926491376873052</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.685304545414361</v>
+        <v>5.698311676831963</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.35876755456507</v>
+        <v>7.371746696963534</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.277136462949692</v>
+        <v>5.290247267324631</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.563918757467142</v>
+        <v>4.576985011767619</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>5.961768219832742</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.196229299663834</v>
+        <v>6.209428038618597</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.197955966487768</v>
+        <v>7.211361094140599</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.993202642170189</v>
+        <v>7.006659935880407</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.101659873589689</v>
+        <v>6.115112162309799</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.298689213262072</v>
+        <v>6.312245259613675</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.079274743069227</v>
+        <v>4.068845107371075</v>
       </c>
     </row>
     <row r="32">
@@ -3569,150 +3569,150 @@
         <v>244</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.654102663396586</v>
+        <v>3.666624953072208</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.042529050432329</v>
+        <v>2.05543886000838</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.647660343835739</v>
+        <v>1.660667475253341</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.646765935459626</v>
+        <v>4.659745077858091</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.009984064649756874</v>
+        <v>0.02309486902469615</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9220821943558946</v>
+        <v>-0.9090392980615292</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.6325283506669095</v>
+        <v>0.6455946049673855</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.444033476475575</v>
+        <v>3.457214485770812</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.792869655867037</v>
+        <v>3.8060683948218</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.582088733134192</v>
+        <v>4.595493860787023</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.197007539964154</v>
+        <v>5.210464833674372</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.411718566162044</v>
+        <v>4.425170854882154</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.991463955217142</v>
+        <v>4.005020001568745</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.9624967629032639</v>
+        <v>0.9520671272051118</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07066</t>
+          <t>X &gt; 0.07065</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>160</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.756561679790025</v>
+        <v>3.769083969465647</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9800119331742323</v>
+        <v>-0.9671021235981812</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.513126491646787</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.130372492836671</v>
+        <v>3.143351635235135</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.408048722235492</v>
+        <v>-2.394937917860553</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.985606784519831</v>
+        <v>-3.972563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.820340501792103</v>
+        <v>-2.807274247491627</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4624760994263895</v>
+        <v>0.4756571087216273</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.901476213244095</v>
+        <v>2.914674952198858</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.426351028216153</v>
+        <v>1.439756155868984</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.471597703898581</v>
+        <v>2.485054997608799</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.039273749700889</v>
+        <v>-1.025717703349287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.664552417424602</v>
+        <v>-2.674982053122754</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.07695</t>
+          <t>X &gt; 0.07694</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>118</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04893456114596262</v>
+        <v>0.06145685082158536</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.799927187411519</v>
+        <v>-5.787017377835468</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.652423012652179</v>
+        <v>-3.639415881234576</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1323393715701044</v>
+        <v>-0.1193602291716402</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-5.755506349354135</v>
+        <v>-5.742395544979196</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.695352547231693</v>
+        <v>-9.682309650937327</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.390255756029397</v>
+        <v>-6.377189501728921</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.833693278281331</v>
+        <v>-1.820494539326567</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.836360836190622</v>
+        <v>-1.822955708537791</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.348716347966381</v>
+        <v>1.362173641676598</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.549103884518701</v>
+        <v>-4.535651595798591</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.816816122582246</v>
+        <v>-5.803260076230643</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.262010044543246</v>
+        <v>-7.272439680241398</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-8.866916695078991</v>
+        <v>-8.85400688550294</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-9.261785401675581</v>
+        <v>-9.248778270257979</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-9.131532269068082</v>
+        <v>-9.118553126669617</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-14.43185824604502</v>
+        <v>-14.41874744167008</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-12.94394011785316</v>
+        <v>-12.93089722155879</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-11.83819764464926</v>
+        <v>-11.82513139034878</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-13.49585723390694</v>
+        <v>-13.4826762246117</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.985428548660671</v>
+        <v>-9.972229809705908</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.645077543212409</v>
+        <v>-9.631672415559578</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.087926105625229</v>
+        <v>-5.074468811915011</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.815447710184557</v>
+        <v>-9.801995421464447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-12.61665470208185</v>
+        <v>-12.60309865573024</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-13.5678391959799</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-9-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-9-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,417 +3904,417 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.09913</t>
+          <t>X &lt; -0.09912</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.018945212493598</v>
+        <v>6.032011466794074</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-0.3874381293736064</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.311744209879073</v>
+        <v>-1.298339082226242</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.680685677813493</v>
+        <v>6.670256042115341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.09284</t>
+          <t>X &lt; -0.09283</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.176664772573531</v>
+        <v>3.189187062249154</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.565091159609274</v>
+        <v>1.578000969185325</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.263005958167327</v>
+        <v>4.276013089584929</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.424186925826369</v>
+        <v>5.437166068224833</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.8857657107542</v>
+        <v>4.898876515129139</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.121351978366761</v>
+        <v>3.134394874661126</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.067546096146039</v>
+        <v>4.080612350446515</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.554276477893197</v>
+        <v>-1.541095468597959</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.646204199127041</v>
+        <v>-2.633005460172278</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4035458790003332</v>
+        <v>-0.3901407513475021</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.48448430183673</v>
+        <v>2.497941595546948</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.673506634439882</v>
+        <v>7.686958923159992</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.222324188443437</v>
+        <v>6.23588023479504</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.472045520719725</v>
+        <v>6.461615885021573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.08655</t>
+          <t>X &lt; -0.08654</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.419605158050892</v>
+        <v>1.829428797051854</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.6775967624779398</v>
+        <v>1.080311669505264</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.630554142837873</v>
+        <v>4.995885112336438</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.282546405880154</v>
+        <v>1.677834393855825</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9950052439746244</v>
+        <v>-0.5845930902743461</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.567128523650261</v>
+        <v>-1.149288026156505</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.08726819386006213</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.988610857095352</v>
+        <v>-2.56313599472665</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.788741178060263</v>
+        <v>-4.34825608228391</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.160605493522972</v>
+        <v>-1.749899016544802</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.626228383057942</v>
+        <v>-1.092531209287756</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.495111296026622</v>
+        <v>4.976329701688258</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.69410988285761</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.919845533084143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.08027</t>
+          <t>X &lt; -0.08025</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>134</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2546323500607244</v>
+        <v>-0.2421100603851016</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.612474619741391</v>
+        <v>-2.59956481016534</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.470268613960513</v>
+        <v>1.483275745378116</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1079844331351865</v>
+        <v>0.1209635755336507</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.922974095369824</v>
+        <v>-1.909863290994885</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.625532157654163</v>
+        <v>-1.612489261359798</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.963997218210018</v>
+        <v>-0.950930963909542</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.834843001634589</v>
+        <v>-3.821437873981758</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.054521699086493</v>
+        <v>-1.041064405376275</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4723987716917719</v>
+        <v>0.485851060411882</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7984128174632872</v>
+        <v>0.8119688638148901</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.540671463172416</v>
+        <v>2.530241827474264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.07398</t>
+          <t>X &lt; -0.07397</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>151</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.811197441379427</v>
+        <v>1.82371973105505</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.787131138472247</v>
+        <v>-1.774221328896196</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.791510088705998</v>
+        <v>1.8045172201236</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.259511565684356</v>
+        <v>1.27249070808282</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.265664616275231</v>
+        <v>-1.252553811900292</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.630474334188705</v>
+        <v>-1.617431437894339</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.715208051460984</v>
+        <v>-1.702141797160508</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.831398072759036</v>
+        <v>-4.818217063463798</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.567894647683069</v>
+        <v>-3.554695908728306</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.431264865823579</v>
+        <v>-2.417859738170748</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.337491743633677</v>
+        <v>1.350949037343895</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.696378212237391</v>
+        <v>2.709830500957501</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.9516202900342066</v>
+        <v>0.9651763363858095</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.525844933568777</v>
+        <v>2.515415297870625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.06769</t>
+          <t>X &lt; -0.06768</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4166145898429292</v>
+        <v>0.429136879518552</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.172077032186849</v>
+        <v>3.185084163604451</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.831430693894873</v>
+        <v>3.844409836293337</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.763908949722179</v>
+        <v>2.777019754097118</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4158482419351941</v>
+        <v>0.4288911382295595</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>-0.7140202792376655</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.310672048721763</v>
+        <v>-3.297491039426525</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.784370347602469</v>
+        <v>-1.771171608647705</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.451756434057316</v>
+        <v>2.465213727767534</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.073441178704329</v>
+        <v>4.086893467424439</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.124086038658902</v>
+        <v>3.137642085010505</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.628000774064766</v>
+        <v>2.834277206136498</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.0614</t>
+          <t>X &lt; -0.06139</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5298174937435078</v>
+        <v>0.5423397834191306</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.778708997058331</v>
+        <v>0.7916188066343821</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.10477052301988</v>
+        <v>4.117777654437482</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.700139934697141</v>
+        <v>4.713119077095605</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.161718719624972</v>
+        <v>4.174829523999911</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.133579261991791</v>
+        <v>2.146622158286156</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2767358506293149</v>
+        <v>-0.2636695963288389</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.209035528480584</v>
+        <v>-1.195854519185346</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1253134225464123</v>
+        <v>0.1385121615011755</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2054207956580214</v>
+        <v>0.2188259233108525</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.791365145759045</v>
+        <v>2.804822439469262</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.825748303104476</v>
+        <v>2.839200591824586</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.214230923196304</v>
+        <v>1.953933459441416</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.80141002388995</v>
+        <v>1.986232900148273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.05511</t>
+          <t>X &lt; -0.0551</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.323355572919795</v>
+        <v>1.335877862595417</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.383537685146386</v>
+        <v>2.396447494722437</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.042104093053602</v>
+        <v>5.055111224471204</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.172357225661102</v>
+        <v>5.185336368059566</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.252256621275961</v>
+        <v>4.265367425650901</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.496263444487802</v>
+        <v>1.509306340782167</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2664915592765951</v>
+        <v>0.2795578135770711</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5823712288178911</v>
+        <v>-0.5691902195226533</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2616917256872071</v>
+        <v>-0.2484929867324439</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.414900646536779</v>
+        <v>0.4283057741896101</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.355185490158128</v>
+        <v>1.368642783868346</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.75981227886853</v>
+        <v>2.548059104162597</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.566495481068344</v>
+        <v>2.353113714275231</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.658806655934477</v>
+        <v>2.805787177646479</v>
       </c>
     </row>
     <row r="14">
@@ -4324,257 +4324,257 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.349533521371221</v>
+        <v>1.362443330947272</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.591028451138271</v>
+        <v>4.604035582555873</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.509160371624553</v>
+        <v>3.522139514023017</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.182860368673602</v>
+        <v>4.195971173048541</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.662120488207442</v>
+        <v>2.675163384501808</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.274356467904859</v>
+        <v>2.287422722205335</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>1.517323775388292</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.746173182941057</v>
+        <v>1.75937192189582</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.502108603973738</v>
+        <v>1.515513731626569</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.688163053442658</v>
+        <v>2.522933785487588</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.207200373439129</v>
+        <v>3.039949867289351</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.580374568341924</v>
+        <v>3.410257906406812</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.401398502820797</v>
+        <v>3.513855867366544</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04254</t>
+          <t>X &lt; -0.04253</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.615369969945462</v>
+        <v>0.6278922596210847</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.0400657870330221</v>
+        <v>0.05297559660907325</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.235870655565968</v>
+        <v>2.24887778698357</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.588921715634605</v>
+        <v>1.601900858033069</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.38210671817901</v>
+        <v>3.395217522553949</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.643279225842868</v>
+        <v>2.656322122137233</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.299478151057635</v>
+        <v>2.312544405358111</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.055092679737271</v>
+        <v>1.068273689032509</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4759580785290609</v>
+        <v>0.4891568174838241</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4030349660399963</v>
+        <v>0.4164400936928274</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.383935366236244</v>
+        <v>1.248008365484452</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.610147527910677</v>
+        <v>2.470731851262819</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.343559148471428</v>
+        <v>2.203448963317378</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.485971142784827</v>
+        <v>2.582850845049563</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03625</t>
+          <t>X &lt; -0.03624</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2393399595542292</v>
+        <v>-0.2268176698786064</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4164873430102958</v>
+        <v>-0.4035775334342446</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.237824278261961</v>
+        <v>1.250831409679563</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.572995443656353</v>
+        <v>1.585974586054817</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.928016851534998</v>
+        <v>4.941127655909938</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.995950592529354</v>
+        <v>4.00899348882372</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.476790645748871</v>
+        <v>2.489856900049347</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.189935115819829</v>
+        <v>1.203116125115066</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9240171968506488</v>
+        <v>0.937215935805412</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4268317233238861</v>
+        <v>-0.5274569588851108</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5117211606887011</v>
+        <v>0.4085662912432895</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.075568490109987</v>
+        <v>0.971079240499094</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.773742779224726</v>
+        <v>0.6688699255166881</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.349422737854901</v>
+        <v>1.426257616298727</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02996</t>
+          <t>X &lt; -0.02995</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6466582981475142</v>
+        <v>0.6591805878231369</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6453906433153023</v>
+        <v>0.6583004528913534</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.988042065543191</v>
+        <v>3.001049196960793</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.957264602337482</v>
+        <v>2.970243744735946</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.15636351608979</v>
+        <v>5.16947432046473</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.038346516607383</v>
+        <v>3.051389412901749</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.148459820269082</v>
+        <v>2.161526074569558</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.037154038234767</v>
+        <v>1.050335047530005</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.228089116469903</v>
+        <v>1.150383486820424</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1460602366168047</v>
+        <v>0.06878841393350399</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3559019110183286</v>
+        <v>0.2778659830692192</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8062239730754541</v>
+        <v>0.7273619525531174</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3162457308185864</v>
+        <v>0.2374508541871805</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6586183142827124</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.02367</t>
+          <t>X &lt; -0.02366</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5652383339722959</v>
+        <v>0.5777606236479187</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.17117922406063</v>
+        <v>-1.158269414484579</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1251193602291778</v>
+        <v>0.06993048665302126</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3237392012221605</v>
+        <v>0.2683516352351418</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.485434987037692</v>
+        <v>2.4267141472208</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.349242650862848</v>
+        <v>1.292160422551476</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.07852884494156598</v>
+        <v>0.02287004359995848</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5713289320201511</v>
+        <v>-0.6267298259517418</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6895187489725387</v>
+        <v>-0.7449162427697047</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.218667887294558</v>
+        <v>-1.274349637581885</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7794468939422714</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4918067493754563</v>
+        <v>-0.5487486682176979</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.474400331979368</v>
+        <v>-1.530616565549039</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.281472569515849</v>
+        <v>-1.235108635401232</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.073262022462664</v>
+        <v>-1.111053016835719</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.850109972389916</v>
+        <v>-1.888380282266155</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.114208412096637</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.226209039579828</v>
+        <v>-1.265382417757984</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.05753633184514229</v>
+        <v>0.01665343773865402</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8704493042048682</v>
+        <v>-0.9102482540071719</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.788936560905405</v>
+        <v>-1.827943538830219</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.908086030751122</v>
+        <v>-1.947372447928615</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.212664951612773</v>
+        <v>-2.251745166144339</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.417522489570402</v>
+        <v>-2.457084910271192</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.777907736259678</v>
+        <v>-1.81830468618567</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.085603297171829</v>
+        <v>-2.12572016358682</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.353074542565118</v>
+        <v>-2.393291960775024</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.950266703138894</v>
+        <v>-1.91556679048648</v>
       </c>
     </row>
     <row r="20">
@@ -4636,205 +4636,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.780284595962748</v>
+        <v>-1.729927888241868</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.24141161596566</v>
+        <v>-2.272481870433623</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.198293338183518</v>
+        <v>-2.230341441844907</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.470501216456412</v>
+        <v>-1.504033467775955</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1385733645248379</v>
+        <v>-0.2557626601285961</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5135503008284985</v>
+        <v>-0.6293099199714973</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.908716297970457</v>
+        <v>-2.021432309445565</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.174476091808671</v>
+        <v>-2.287657676651989</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.432455206213646</v>
+        <v>-2.545249471031056</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.442364055582722</v>
+        <v>-2.557059130755214</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.80555884562218</v>
+        <v>-1.922315520319486</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.647696197109305</v>
+        <v>-1.764857121168248</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.944273749700891</v>
+        <v>-2.06173127078744</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.890933522308515</v>
+        <v>-1.952138602643515</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.004804</t>
+          <t>X &lt; -0.0048</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.822511802638083</v>
+        <v>-1.810845832704096</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.186853365399294</v>
+        <v>-2.176393311337641</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.292586973743958</v>
+        <v>-2.282400664902745</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.808808044935411</v>
+        <v>-1.863042226657441</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8401435332540643</v>
+        <v>-0.8962175083915795</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.661888835801882</v>
+        <v>-1.716641993219064</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.418239796211608</v>
+        <v>-2.472152530643456</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.595129805580029</v>
+        <v>-2.649342891278373</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.493915565818213</v>
+        <v>-2.548362251136616</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.410409897233713</v>
+        <v>-2.465892111139986</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.130492328255755</v>
+        <v>-2.186589189931347</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.061264956001807</v>
+        <v>-2.117456310190121</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.867106975715053</v>
+        <v>-1.924029600455391</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.646511180311194</v>
+        <v>-1.663077291217988</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001484</t>
+          <t>X &lt; 0.001488</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.467836681705109</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.670585703666028</v>
+        <v>-2.684012005830645</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.424022105685737</v>
+        <v>-2.437693180484374</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.831165968701789</v>
+        <v>-2.844603259690537</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.957817834600803</v>
+        <v>-1.971860994783626</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.300545182877123</v>
+        <v>-2.314341723012539</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.28291112326103</v>
+        <v>-3.296237286506006</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.15841290365686</v>
+        <v>-3.171941761334871</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.5011587481955</v>
+        <v>-3.514538819640812</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.655953498532817</v>
+        <v>-3.669498342845657</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.524928286837394</v>
+        <v>-3.538607553831532</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.154420786541777</v>
+        <v>-3.168292017302988</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.929085702302636</v>
+        <v>-2.943199680692231</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.65166581948646</v>
+        <v>-2.638274170587977</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.007773</t>
+          <t>X &lt; 0.007776</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.228654560280589</v>
+        <v>-2.238304649855039</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.625983235602483</v>
+        <v>-2.635791443986534</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.335569685707213</v>
+        <v>-2.345593155152336</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.491589504511971</v>
+        <v>-2.501524689853198</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.857650844251403</v>
+        <v>-1.867982548881322</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.934799619548578</v>
+        <v>-1.945043994326255</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.836933422146089</v>
+        <v>-2.846803216974166</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.661417216199986</v>
+        <v>-2.671466785083688</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.876313866472479</v>
+        <v>-2.886287863206199</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.260179764872007</v>
+        <v>-3.270164127567675</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.909607969860289</v>
+        <v>-2.919796575275562</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.629828451394573</v>
+        <v>-2.640141318120982</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.627006668955545</v>
+        <v>-2.637413933947954</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.442071281161837</v>
+        <v>-2.432080544693299</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.541242439914605</v>
+        <v>-1.548515098133421</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.888837749659459</v>
+        <v>-1.896221828223126</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.563280095235626</v>
+        <v>-1.570854845833786</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.645892098603007</v>
+        <v>-1.653420048934436</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.657756779845457</v>
+        <v>-1.665365933424752</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.845809276731664</v>
+        <v>-1.85330542189616</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.572239605804583</v>
+        <v>-2.579470509173873</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.668369574774694</v>
+        <v>-2.675638177604817</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.669917548939146</v>
+        <v>-2.677199560661627</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.070528846978846</v>
+        <v>-3.077787703780132</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.630333626573524</v>
+        <v>-2.637799916587774</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.65307456420485</v>
+        <v>-2.660531734936384</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.622883667701672</v>
+        <v>-2.630421060101817</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.586427417424595</v>
+        <v>-2.578828206968907</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9298524967214448</v>
+        <v>-0.9352404487351222</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9246156870845539</v>
+        <v>-0.9301841249880383</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9880586648055854</v>
+        <v>-0.9936514019924232</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.256584028902452</v>
+        <v>-1.262072565043027</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.15021991221461</v>
+        <v>-1.155807483077943</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.182134804011653</v>
+        <v>-1.187682190243557</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.700911532432777</v>
+        <v>-1.70629095476626</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.731663573161555</v>
+        <v>-1.737086623868898</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.913419257139189</v>
+        <v>-1.918788997644405</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.187277413749676</v>
+        <v>-2.192648025315677</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.024566870717877</v>
+        <v>-2.030019941394336</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.006139822397429</v>
+        <v>-2.011598928139087</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.233010665262647</v>
+        <v>-2.238440061214654</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.173714721089524</v>
+        <v>-2.168178145237199</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8571891068682547</v>
+        <v>-0.8609097392477807</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.004602742113484</v>
+        <v>-1.008401683069543</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.256807591911873</v>
+        <v>-1.260559375523506</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.645218058344426</v>
+        <v>-1.648839800533118</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.347872288713127</v>
+        <v>-1.351630831246375</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.506289104091216</v>
+        <v>-1.509977246763583</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.889539745171682</v>
+        <v>-1.893115722436477</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.803961932740116</v>
+        <v>-1.80760266429224</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.942766688964113</v>
+        <v>-1.946370459343257</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.050297756889549</v>
+        <v>-2.053934695866019</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.985473003172125</v>
+        <v>-1.98914822107217</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.060249009295937</v>
+        <v>-2.063900183369213</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.463389352985793</v>
+        <v>-2.466947573889236</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.291329668609436</v>
+        <v>-2.287268850343217</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9110662409434838</v>
+        <v>-0.9137959832250644</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.146432051517422</v>
+        <v>-1.149185826644612</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.28887146545889</v>
+        <v>-1.291607236163877</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.468502581171606</v>
+        <v>-1.471179291074421</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.162120383473273</v>
+        <v>-1.164920155871208</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.144966974093293</v>
+        <v>-1.147756366756703</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.450896057347663</v>
+        <v>-1.453601261709643</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.576276123454463</v>
+        <v>-1.578972520908003</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.473153196776664</v>
+        <v>-1.475885213776252</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.654906385781459</v>
+        <v>-1.657634890677109</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.635862990257458</v>
+        <v>-1.638610482818251</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.822654153592786</v>
+        <v>-1.825345847366044</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.137708003188564</v>
+        <v>-2.140331946672724</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.049944341415099</v>
+        <v>-2.046828298299367</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.864081561921509</v>
+        <v>-0.8661851523473842</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.100476785781936</v>
+        <v>-1.102586680129775</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.111732071582558</v>
+        <v>-1.113857635337347</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.420109639891621</v>
+        <v>-1.42214311951394</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.035708296703575</v>
+        <v>-1.037876091428338</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.9216170001838506</v>
+        <v>-0.9238050229772412</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.133035647974346</v>
+        <v>-1.135168685630113</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.215902662640623</v>
+        <v>-1.218034347423703</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.147977067074002</v>
+        <v>-1.150131975683038</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.27251260814748</v>
+        <v>-1.274671563528905</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.319607183853627</v>
+        <v>-1.321763184209381</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.525429030740071</v>
+        <v>-1.527526213491406</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.901692003894809</v>
+        <v>-1.90370235371882</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.750161063613454</v>
+        <v>-1.74770027888335</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3649</v>
+        <v>3650</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4999921159500147</v>
+        <v>-0.5016640512823685</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6223569208825097</v>
+        <v>-0.6240518778308441</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7567112408637158</v>
+        <v>-0.7583840246056113</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.295016957832907</v>
+        <v>-1.296539075147372</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8894593291244988</v>
+        <v>-0.8911117358436087</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9327287424088126</v>
+        <v>-0.9343599516481049</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.002780326737408</v>
+        <v>-1.004396205380615</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.154315966237085</v>
+        <v>-1.155907442700695</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.036331668529307</v>
+        <v>-1.037958426734114</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.159879467266997</v>
+        <v>-1.161502738493347</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.157920368390577</v>
+        <v>-1.159552174578444</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.1906091141052</v>
+        <v>-1.192231691218794</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.349205256550199</v>
+        <v>-1.350799872617984</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.248753568424874</v>
+        <v>-1.246899861341937</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3764</v>
+        <v>3765</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4150692442237442</v>
+        <v>-0.416331594324717</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4768339670725368</v>
+        <v>-0.4781227749087478</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7250462026847302</v>
+        <v>-0.7262802880142374</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.083988927407098</v>
+        <v>-1.085125185956912</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7866599069691205</v>
+        <v>-0.787889693165269</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7134699870648973</v>
+        <v>-0.7147120461899448</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7308748428157088</v>
+        <v>-0.7321151806835786</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.8654416724569032</v>
+        <v>-0.8666592529861461</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7528419082735596</v>
+        <v>-0.7540916260504815</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7923326235885071</v>
+        <v>-0.7935948656221186</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7700402042511385</v>
+        <v>-0.7713144291427909</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7474710771521629</v>
+        <v>-0.7487510815198135</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.80770004452161</v>
+        <v>-0.8089758021278328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6759764344277954</v>
+        <v>-0.6746500478106654</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3854</v>
+        <v>3855</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4117212268559598</v>
+        <v>-0.4126637037504821</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.354365269956439</v>
+        <v>-0.3553552914285447</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4765947406763829</v>
+        <v>-0.4775615580169514</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.617039515444894</v>
+        <v>-0.6179678990468744</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4426073554221333</v>
+        <v>-0.4435921621669721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3123157436083943</v>
+        <v>-0.3133288377465675</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3829861894377942</v>
+        <v>-0.3839832065801971</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4993114653404476</v>
+        <v>-0.5002882422237249</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5202327787227361</v>
+        <v>-0.5212058768166941</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.6044939691918216</v>
+        <v>-0.605462812775734</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5874507793785781</v>
+        <v>-0.5884286726866961</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.512691337926114</v>
+        <v>-0.5136884471320613</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5293839961340936</v>
+        <v>-0.5303857531418146</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3429385097961628</v>
+        <v>-0.3419729740047259</v>
       </c>
     </row>
     <row r="32">
@@ -5260,153 +5260,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3934</v>
+        <v>3935</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2258933493460304</v>
+        <v>-0.226610052824114</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1262993127991621</v>
+        <v>-0.1270653868360867</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1019085231675234</v>
+        <v>-0.1026869903603185</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.287477405743445</v>
+        <v>-0.288207300126075</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.0006178320503522627</v>
+        <v>-0.001428790071507535</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05707459549031313</v>
+        <v>0.05625300246689591</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.03916186692786283</v>
+        <v>-0.03996070106849459</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2132853218934088</v>
+        <v>-0.2140472810271703</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2349480061009217</v>
+        <v>-0.2357057584610516</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2839079865121334</v>
+        <v>-0.2846662863752343</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3220903834775939</v>
+        <v>-0.3228424122439222</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2734906834714366</v>
+        <v>-0.2742549374120529</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.247501195698355</v>
+        <v>-0.2482786789590463</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.05969730812110186</v>
+        <v>-0.05903542034003806</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07066</t>
+          <t>X &lt; 0.07065</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1491068888033737</v>
+        <v>-0.1495668241851433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.03890866235926893</v>
+        <v>0.03838658888011537</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.01986078372713962</v>
+        <v>-0.02037226765843059</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1243444882953924</v>
+        <v>-0.1248290547623725</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.09567613497831928</v>
+        <v>0.09513159554560957</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1583947057931283</v>
+        <v>0.1578371547345512</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1121129143569561</v>
+        <v>0.1115657922500475</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01838871170681955</v>
+        <v>-0.0189081086696774</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1153955242652387</v>
+        <v>-0.1158916481987688</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05674196034674139</v>
+        <v>-0.05726099551057473</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.0983475833433971</v>
+        <v>-0.09885847827384708</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0002380442286238349</v>
+        <v>-0.0007732663502295622</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.04137442148597614</v>
+        <v>0.04082458520792898</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1061046258805192</v>
+        <v>0.1064934382930218</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.07695</t>
+          <t>X &lt; 0.07694</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.00141769659102664</v>
+        <v>-0.001780046243723632</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1680725461970809</v>
+        <v>0.1676572675140235</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1058673337000613</v>
+        <v>0.1054644091320469</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.003836866301050179</v>
+        <v>0.003459716787588718</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1669082696544066</v>
+        <v>0.1664871435645097</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2812319568764252</v>
+        <v>0.2807846003466636</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1854069779226677</v>
+        <v>0.1849823896765059</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1498223857028265</v>
+        <v>0.1494031131474998</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.05322898077175608</v>
+        <v>0.05283284693570067</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.05331953215316076</v>
+        <v>0.05291728748030522</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0391702015899682</v>
+        <v>-0.03955130160380804</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1321502359362796</v>
+        <v>0.1317270214876274</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1690185428378967</v>
+        <v>0.1685831336768118</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2110633461221951</v>
+        <v>0.2113144255770791</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.00230066201549306</v>
+        <v>0.002044047362439017</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1813981983406308</v>
+        <v>0.1810899874317613</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1895225270988448</v>
+        <v>0.1892102714811656</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1869027072616234</v>
+        <v>0.1865915865140764</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2954609048666299</v>
+        <v>0.2951205616716166</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2650636201608094</v>
+        <v>0.2647319928371701</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2424795420996304</v>
+        <v>0.2421528612358159</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2765004896702976</v>
+        <v>0.2761630828742696</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2046294213436255</v>
+        <v>0.2043090985403211</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1977029071815082</v>
+        <v>0.1973799665545215</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1043167666274059</v>
+        <v>0.1040154661300363</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2012933612440122</v>
+        <v>0.2009684196736643</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2588031733760303</v>
+        <v>0.2584619841507134</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2781686377781298</v>
+        <v>0.2783146501739466</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_9_21.xlsx
@@ -568,1145 +568,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.09598</t>
+          <t>X ≈ -0.09585</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.69660827357318</v>
+        <v>14.11162874106251</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.424493096899702</v>
+        <v>4.22757717791351</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.70412524934068</v>
+        <v>12.14681962270534</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5095649019476198</v>
+        <v>3.966215457662912</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-16.39761602599098</v>
+        <v>-13.15114861711886</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.427399174829951</v>
+        <v>-12.88198044272997</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.514039651551002</v>
+        <v>-12.94568699354849</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.982282306086354</v>
+        <v>-5.092600219840193</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.045358198717047</v>
+        <v>-5.130744753846436</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.472880825920193</v>
+        <v>2.370134013785773</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.269612560097286</v>
+        <v>2.166667970383997</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.99376704899668</v>
+        <v>10.55456399999414</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>12.57694405730616</v>
+        <v>10.16212611229374</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.113479485338786</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.08969</t>
+          <t>X ≈ -0.08957</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.096430118338532</v>
+        <v>-5.125573446531483</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.456332348442977</v>
+        <v>-1.457526555081522</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.647335430008717</v>
+        <v>8.647246974821847</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-17.47185796479745</v>
+        <v>-17.47246534142001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-28.51623907802064</v>
+        <v>-28.46797149395329</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-22.97352827610005</v>
+        <v>-22.94974004110629</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.80965213526687</v>
+        <v>-17.76180656759995</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.769394452661267</v>
+        <v>-7.720252250039842</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-13.08887758178131</v>
+        <v>-13.01575624587988</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.683265049111391</v>
+        <v>-8.584040586118164</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-19.40855282942859</v>
+        <v>-19.30875847999155</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-8.857875405714196</v>
+        <v>-8.734252201465367</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.280049074295505</v>
+        <v>-9.131402848665495</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-9.056561000488777</v>
+        <v>-8.884562240924517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.08339</t>
+          <t>X ≈ -0.08328</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.54865121309615</v>
+        <v>-13.57786789604855</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-26.23658146611156</v>
+        <v>-26.23797462730008</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-21.09655689043849</v>
+        <v>-21.09686294025275</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.887877363476271</v>
+        <v>-9.888436100730914</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-10.42725609744127</v>
+        <v>-10.37888369332823</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.58842436300705</v>
+        <v>-4.564540366092444</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-10.22016765557293</v>
+        <v>-10.17228879832231</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-21.78358929623061</v>
+        <v>-21.73450463174783</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-10.75243631672585</v>
+        <v>-10.67930879599304</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-17.15434209674031</v>
+        <v>-17.05514166137834</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7088406139101124</v>
+        <v>-0.609010070227896</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-28.43879807492423</v>
+        <v>-28.31520188966875</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-17.75746490276905</v>
+        <v>-17.60882481040019</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293558614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.07711</t>
+          <t>X ≈ -0.077</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>18.04909327533509</v>
+        <v>19.64888124772981</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.717628579061909</v>
+        <v>6.997282487312596</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.324711794600965</v>
+        <v>6.605955674018922</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.32359448519725</v>
+        <v>12.27910509901069</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.919973914082085</v>
+        <v>6.250923645189587</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.652998518877958</v>
+        <v>0.9801110707364984</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.61017084530944</v>
+        <v>-4.626191297934724</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.204628744412162</v>
+        <v>0.4550340918970122</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.48399870570519</v>
+        <v>11.51554964141736</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.63718695168194</v>
+        <v>10.69529719105137</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>20.19063119039232</v>
+        <v>21.59671878440862</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>20.22996872601907</v>
+        <v>21.66016941236176</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.172265740827079</v>
+        <v>4.607933955081656</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.398547358639277</v>
+        <v>4.858127817557545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.07082</t>
+          <t>X ≈ -0.07072</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.096113133078759</v>
+        <v>-6.543161349332507</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.455944954658044</v>
+        <v>-2.733574348733271</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.646996403718077</v>
+        <v>7.65387645806927</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.02912429496683</v>
+        <v>13.17734281414995</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18.74709161355094</v>
+        <v>18.0859736597962</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.543322709681235</v>
+        <v>7.573508911277301</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.206948121578051</v>
+        <v>2.118875494397365</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.741542540509201</v>
+        <v>1.654430789826115</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.309504009534677</v>
+        <v>4.317145064325345</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.090633265183691</v>
+        <v>6.1951477440752</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.8877329381612</v>
+        <v>5.992583097707865</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.554066933659747</v>
+        <v>8.75356057847376</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>11.76737664507304</v>
+        <v>11.06276131321447</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.101333736350931</v>
+        <v>0.5037734632006661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.06454</t>
+          <t>X ≈ -0.06443</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.416310031563263</v>
+        <v>1.331625433187753</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>19.68658951649644</v>
+        <v>18.92674029670773</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.3107638747529</v>
+        <v>10.86710080691414</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.44994952149658</v>
+        <v>10.99934555274655</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14.88421842420637</v>
+        <v>14.35158155735736</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.19248722998151</v>
+        <v>14.62768042799705</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.12440738170956</v>
+        <v>3.0527245629806</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>14.62020499413824</v>
+        <v>14.10960764337886</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.56330292190623</v>
+        <v>14.07609627391535</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.692102417197056</v>
+        <v>5.57197724725156</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.486298398034457</v>
+        <v>5.36928090278559</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.470466720376983</v>
+        <v>-6.103899110603642</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.910802895030642</v>
+        <v>-6.500431871219902</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.424982053122754</v>
+        <v>-6.252983293554337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.05825</t>
+          <t>X ≈ -0.05815</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.060198586834971</v>
+        <v>2.583283468421328</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.924870255232307</v>
+        <v>9.14393806117517</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.528468688934218</v>
+        <v>8.753132115213418</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.494886729599472</v>
+        <v>6.849253432743538</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.777233946202124</v>
+        <v>4.326840099968095</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.432100744529379</v>
+        <v>-1.509544744172736</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.820741902269297</v>
+        <v>2.504150472157725</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.343676619419931</v>
+        <v>2.039739172747502</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.060988360044881</v>
+        <v>-0.0349971200103667</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.416236327190177</v>
+        <v>3.219479272158331</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.309562262935891</v>
+        <v>-3.101562423314782</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.246027681745225</v>
+        <v>3.075155083566827</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.218847514043013</v>
+        <v>4.72123012524299</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.618496207746816</v>
+        <v>4.971506502362274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05196</t>
+          <t>X ≈ -0.05187</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>67</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.021657006848656</v>
+        <v>1.216928959245344</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.652431932053005</v>
+        <v>-1.849221657054848</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.907139379415099</v>
+        <v>3.710399509993621</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.919295798049546</v>
+        <v>-2.113748048346942</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.984825389308774</v>
+        <v>4.843141181677154</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.266055662336655</v>
+        <v>8.095970254766499</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.16292001038725</v>
+        <v>11.01735907058116</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9.691089038563256</v>
+        <v>10.55519307468055</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.632041838735205</v>
+        <v>9.030321759155392</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.788520254957277</v>
+        <v>5.227654976266123</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.075749484358802</v>
+        <v>6.516370872028645</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.963463000710391</v>
+        <v>3.592656403674241</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.528386774262657</v>
+        <v>6.182891707719833</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.261585111056355</v>
+        <v>6.433583870622336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.04568</t>
+          <t>X ≈ -0.04559</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6935665256142087</v>
+        <v>-1.595848860376215</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.645679514230999</v>
+        <v>-8.611979813461581</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-11.60610053261637</v>
+        <v>-12.63348215469091</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-9.696465904141121</v>
+        <v>-10.69348868794035</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.321987094260912</v>
+        <v>-2.114999704505571</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.541643982308116</v>
+        <v>1.785765218633472</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.457786745238479</v>
+        <v>1.725809581102446</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.576770839974749</v>
+        <v>-2.369314807697855</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.992434598105561</v>
+        <v>-7.854237991591908</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.058681967963665</v>
+        <v>-6.862927935973815</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.264945002390391</v>
+        <v>-7.068738859640128</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.8734239928930165</v>
+        <v>-1.560735178406148</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.865003417635819</v>
+        <v>-5.591542101757476</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-3.525710566282534</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03939</t>
+          <t>X ≈ -0.0393</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.486610755364353</v>
+        <v>-2.985275411678757</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.147728371798635</v>
+        <v>-1.660736711682354</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.544452556166888</v>
+        <v>-2.054412612160661</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.53965623829594</v>
+        <v>1.947835841492541</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>10.88639669512073</v>
+        <v>11.14507539131966</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.210709641201355</v>
+        <v>8.514198874115095</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.191702390444433</v>
+        <v>2.641841889241682</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.730445872060415</v>
+        <v>1.208441628914549</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.658638896663845</v>
+        <v>2.141515303684976</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.13962908052067</v>
+        <v>-4.499779034619621</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.799598467738186</v>
+        <v>-3.734935774385427</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.745418335184844</v>
+        <v>-5.618530968620973</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.165569188497358</v>
+        <v>-6.01502213415381</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.959635518469284</v>
+        <v>-3.82579882753712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.03309</t>
+          <t>X ≈ -0.03302</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.930698207404937</v>
+        <v>3.366091738726162</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.579722394718118</v>
+        <v>3.954318200152272</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.479295121631047</v>
+        <v>9.560910549618143</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.100270304341194</v>
+        <v>8.95127708365623</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.050240860581617</v>
+        <v>5.861896259370212</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4617769719064597</v>
+        <v>1.287369886375643</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9658347417928042</v>
+        <v>2.376553634342756</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4944848680955474</v>
+        <v>1.553733187470783</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.948109951542826</v>
+        <v>2.679844301121584</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.273089489201986</v>
+        <v>2.262581583428577</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2043389417849681</v>
+        <v>-0.5255280666139228</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1699607894294672</v>
+        <v>-0.4675654572531585</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.34768740031933</v>
+        <v>-1.614370561089075</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.879527507668037</v>
+        <v>-2.117644947691602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.02681</t>
+          <t>X ≈ -0.02674</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3108001229312194</v>
+        <v>-0.6232277771546748</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-7.675305316379614</v>
+        <v>-7.682073616618617</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-10.37071360007539</v>
+        <v>-10.26212801201512</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.352041643461945</v>
+        <v>-10.38300429238848</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.285626509645567</v>
+        <v>-8.688433767219486</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.955026772038842</v>
+        <v>-6.231419389246128</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.605328849223348</v>
+        <v>-8.477668314404049</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.614666626717167</v>
+        <v>-6.762272964544948</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.509175622513794</v>
+        <v>-7.891632798614388</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-6.53600643899847</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.540807071356845</v>
+        <v>-5.102725429396671</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.081141562679555</v>
+        <v>-5.830251331486039</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.800142990705737</v>
+        <v>-8.958394387701105</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.149119984157366</v>
+        <v>-9.258447774430287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.02052</t>
+          <t>X ≈ -0.02046</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.296847000103448</v>
+        <v>-6.228460189814498</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.568658204470012</v>
+        <v>-4.614918516297621</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.628426019768746</v>
+        <v>-6.141155791836105</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.868063889878911</v>
+        <v>-6.470740660617423</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.776216456673232</v>
+        <v>-8.342750397450224</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.935463431604461</v>
+        <v>-8.991079631569789</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-8.563552786304314</v>
+        <v>-8.594171627127636</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.747516407260008</v>
+        <v>-7.222128747526462</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.721740572915408</v>
+        <v>-8.181576692693412</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.745175350980325</v>
+        <v>-7.63189664264938</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.580013495541884</v>
+        <v>-5.993807584308485</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-7.828740366017612</v>
+        <v>-8.238971962526549</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.509165191933654</v>
+        <v>-5.612624511942542</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.370187532574704</v>
+        <v>-4.179250574662085</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.01423</t>
+          <t>X ≈ -0.01418</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.332767882386015</v>
+        <v>-4.381416744185323</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.886340806725748</v>
+        <v>-3.680065769546971</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.750247993949927</v>
+        <v>-6.55314260083707</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.504796512913096</v>
+        <v>-2.704250295159397</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.396995531029276</v>
+        <v>-1.540606874127924</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5464690335852396</v>
+        <v>0.3850712066744677</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.830422395639786</v>
+        <v>-3.394593147013616</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.709013673171377</v>
+        <v>-4.273649047892924</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.769995829694054</v>
+        <v>-4.310621657029721</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.973824091044683</v>
+        <v>-3.068334535365551</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.355479981815073</v>
+        <v>-2.446028701909803</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.263488660735554</v>
+        <v>-0.3217462620655809</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6836395140487852</v>
+        <v>-0.7169041886293073</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.103994398801959</v>
+        <v>-2.120751888597418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.007945</t>
+          <t>X ≈ -0.007897</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.149790202719856</v>
+        <v>-2.181164456465936</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.774221328896196</v>
+        <v>-1.461709962674419</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.500118541465802</v>
+        <v>-1.855447950989046</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.363270881321142</v>
+        <v>-2.712406015037594</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.570434606602277</v>
+        <v>-2.872707787568466</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-6.253193027298309</v>
+        <v>-5.56044858453901</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.35114841967706</v>
+        <v>-3.976367831659211</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.155965407834657</v>
+        <v>-3.455358486779311</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.56131842528459</v>
+        <v>-1.847594253810854</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.086733910356095</v>
+        <v>-1.355633360941624</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.284812552060004</v>
+        <v>-2.546615913740943</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.58156022751924</v>
+        <v>-2.817396544797099</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.352704458316246</v>
+        <v>-0.5809755239925067</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4647171524604303</v>
+        <v>0.3259640748648778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.001656</t>
+          <t>X ≈ -0.001612</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>387</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.19409432510794</v>
+        <v>-4.96489218664415</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.738096955639584</v>
+        <v>-4.739283742084176</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.065684877862267</v>
+        <v>-3.324236200683117</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.811428726522024</v>
+        <v>-7.070321151716563</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.316126548351505</v>
+        <v>-6.525978561402276</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.726762854633733</v>
+        <v>-4.961203378500656</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.620258743615722</v>
+        <v>-6.83064499744188</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.278541857686641</v>
+        <v>-5.487692228109459</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.406707476741659</v>
+        <v>-7.850246232595097</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-8.515024205888118</v>
+        <v>-8.932472746226615</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.978123296964903</v>
+        <v>-9.136613193762706</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.393357547710238</v>
+        <v>-7.528058859498586</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-7.03831460257409</v>
+        <v>-7.148022987612798</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.554181019530965</v>
+        <v>-6.898978125597374</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.004632</t>
+          <t>X ≈ 0.00467</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>313</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7237275321318677</v>
+        <v>-0.4334345085930522</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.334913625195554</v>
+        <v>-2.016611593748905</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.771218556276544</v>
+        <v>-1.771371946280865</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3630381411226153</v>
+        <v>-0.04404381560924264</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.220816512109757</v>
+        <v>-0.8527817744526089</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3545127890908972</v>
+        <v>0.05898138014906351</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.04968638806663961</v>
+        <v>0.3178141088150497</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4417114218206706</v>
+        <v>0.4909589842142381</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.019706901080639</v>
+        <v>1.412452828751569</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7886783489233409</v>
+        <v>-0.6893310236287675</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9235534001646428</v>
+        <v>0.7039726182920063</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.6384427346285904</v>
+        <v>0.4426505377655303</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7401745723588675</v>
+        <v>-0.9109738424724156</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.153416557915236</v>
+        <v>-1.300906616239793</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.01092</t>
+          <t>X ≈ 0.01095</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.545142601387475</v>
+        <v>3.081993438270977</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.562621003437656</v>
+        <v>3.143553195220314</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.145048315751019</v>
+        <v>4.065604680589828</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.601006358362184</v>
+        <v>4.195488721804509</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1718108820299733</v>
+        <v>-0.5700762086211313</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.177368448486163</v>
+        <v>-0.9551854266443129</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.6106130097066185</v>
+        <v>-0.6868941474487613</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.706346148607359</v>
+        <v>-2.797463749937208</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.138663810016212</v>
+        <v>-1.189699516968744</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.662849707323232</v>
+        <v>-1.355633360941731</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5646192694921126</v>
+        <v>-0.2439843347935735</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.810371410296462</v>
+        <v>-2.488449176376051</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.579056465564271</v>
+        <v>-2.225712366097774</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.656252411428866</v>
+        <v>-2.963509609345557</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.0172</t>
+          <t>X ≈ 0.01724</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.240395444875489</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.219373286237889</v>
+        <v>7.27034745359353</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.873782229351697</v>
+        <v>3.305180893850256</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.036794258185957</v>
+        <v>1.811688311688307</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.13784896738543</v>
+        <v>3.270491118788378</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.418829554397519</v>
+        <v>4.517302611633276</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.645594604967386</v>
+        <v>5.43067249643375</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.162132518557698</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.461806099739839</v>
+        <v>3.953841152887641</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.251231565705098</v>
+        <v>4.753389195449316</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.079317292690803</v>
+        <v>2.601196799861242</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.44156429750511</v>
+        <v>2.98403886190146</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.054200329437606</v>
+        <v>0.6408289872857225</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.279935979664138</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0235</t>
+          <t>X ≈ 0.02352</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1475826972009742</v>
+        <v>-0.6582599730350935</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.758768790264881</v>
+        <v>-1.904736721490686</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.820206841686549</v>
+        <v>-3.308575719906365</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.356648364764858</v>
+        <v>-5.198893698893706</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.228271251193881</v>
+        <v>-3.331240482943223</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.741956647626019</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.682274247491598</v>
+        <v>-3.455811390050101</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.482676224611708</v>
+        <v>-1.901442130231452</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.210325047801192</v>
+        <v>-1.601714402667952</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7269105107976728</v>
+        <v>-0.06864062658053882</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.598278335724572</v>
+        <v>-0.9461817475173007</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.563900183369213</v>
+        <v>-1.898116020253426</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.650717703349329</v>
+        <v>-3.976775630319004</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.424982053122754</v>
+        <v>-2.717629758202555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.02978</t>
+          <t>X ≈ 0.0298</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.741999774376765</v>
+        <v>-2.019915746455666</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.353185867440487</v>
+        <v>-3.112896753180038</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.777513902441889</v>
+        <v>-1.545850427769338</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.308376265777014</v>
+        <v>1.52521008403361</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.755308387558109</v>
+        <v>2.016353099944375</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.515736604385403</v>
+        <v>4.740119010920225</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.416247919995996</v>
+        <v>5.659855078557449</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.252845847585931</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.873418794563442</v>
+        <v>6.1374418659002</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.530889160795105</v>
+        <v>4.823417206653737</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.833577165096486</v>
+        <v>4.129080680686293</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.897511967698051</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.955193626700037</v>
+        <v>3.301893413056042</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.703096764611288</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.03607</t>
+          <t>X ≈ 0.03608</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2217866721683421</v>
+        <v>0.5511126649089348</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.03804806954408946</v>
+        <v>-0.3517923114033437</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.945558924079215</v>
+        <v>2.65583024449964</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.302594310710802</v>
+        <v>-0.6156462585034035</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.861818838896205</v>
+        <v>1.616193035918819</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.186219895558281</v>
+        <v>3.929794881268364</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.12853656331913</v>
+        <v>5.909955118573471</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.012819270883789</v>
+        <v>6.804666575877249</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.276161438685342</v>
+        <v>6.087421857896871</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.4532696693825</v>
+        <v>7.304409603612584</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.89721715977096</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.255919636450678</v>
+        <v>5.117619566910733</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.484417431785886</v>
+        <v>3.361917422659864</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.061504433363616</v>
+        <v>4.971506502362232</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>133</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.173219307811507</v>
+        <v>9.144023513458876</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>12.07331141023633</v>
+        <v>12.07212462379167</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.67102122848884</v>
+        <v>8.670867838484519</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.034329078844166</v>
+        <v>2.033834586466163</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.999798924244757</v>
+        <v>3.048344844010529</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.214105241608877</v>
+        <v>-1.190147832659264</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.460582895365548</v>
+        <v>2.508594574355868</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.4897548530825233</v>
+        <v>0.5390024154762401</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.834492997974209</v>
+        <v>1.933840323268782</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.133551238210302</v>
+        <v>3.233459274228977</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.679207586054353</v>
+        <v>7.802904207082598</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>13.27409432672586</v>
+        <v>13.42278387450369</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.99607057845623</v>
+        <v>12.1680693380229</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>115</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.30169266511782</v>
+        <v>2.272496870765188</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.168767441619238</v>
+        <v>4.167580655174582</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2957351872990017</v>
+        <v>0.2955817972946804</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.643351635235199</v>
+        <v>5.642857142857196</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.496366429965484</v>
+        <v>2.544912349731256</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.272001329165789</v>
+        <v>6.295958738115402</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.926421404682308</v>
+        <v>7.974433083672629</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.328917978286803</v>
+        <v>8.37816554068052</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.26793582176407</v>
+        <v>8.341192931543766</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.89627789499947</v>
+        <v>10.99562522029404</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.56114195413053</v>
+        <v>11.66104999014921</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.33465054126842</v>
+        <v>13.45834716229667</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.39276055752032</v>
+        <v>16.54145010529815</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.48806142513811</v>
+        <v>17.66006018470477</v>
       </c>
     </row>
     <row r="30">
@@ -1823,254 +1823,254 @@
         <v>90</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.258693808312124</v>
+        <v>-0.2878896026647553</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.79678676529074</v>
+        <v>4.795599978846084</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9.957570936091223</v>
+        <v>9.957417546086901</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>18.97668496856841</v>
+        <v>18.97619047619041</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.99395097102833</v>
+        <v>14.04249689079411</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>16.51354722288565</v>
+        <v>16.53750463183526</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.20661464139725</v>
+        <v>14.25462632038757</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>14.85065710872168</v>
+        <v>14.8999046711154</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.234119396643322</v>
+        <v>9.307376506423019</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.27308948920232</v>
+        <v>7.372436814496893</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.068388330942128</v>
+        <v>7.168296366960803</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.32498870551975</v>
+        <v>9.448685326547995</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.12706007442843</v>
+        <v>11.27574962220626</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.57501794687725</v>
+        <v>13.74701670644391</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.06123</t>
+          <t>X ≈ 0.06121</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>80</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.769083969465655</v>
+        <v>8.739888175113023</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.90789787640182</v>
+        <v>10.90671108995716</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.01312649164678</v>
+        <v>18.01297310164246</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.64335163523514</v>
+        <v>15.64285714285714</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21.35506208213945</v>
+        <v>21.40360800190522</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>17.90243611177453</v>
+        <v>17.92639352072415</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.56772575250834</v>
+        <v>16.61573743149866</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.6006571087216</v>
+        <v>13.64990467111532</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.53967495219882</v>
+        <v>13.61293206197852</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>15.18975615586899</v>
+        <v>15.28910348116356</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.4850549976088</v>
+        <v>12.58496303362747</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.26943314996412</v>
+        <v>11.39312977099237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.34928229665071</v>
+        <v>13.49797184442854</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.57501794687725</v>
+        <v>13.74701670644391</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.06751</t>
+          <t>X ≈ 0.06749</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>84</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.471464921846604</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.846459824980094</v>
+        <v>3.846306434975773</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.548113539997061</v>
+        <v>7.547619047619058</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.22248765727025</v>
+        <v>7.270499336260571</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.136371394435947</v>
+        <v>9.185618956829664</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.503960666484552</v>
+        <v>5.577217776264249</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.60642282253568</v>
+        <v>10.70577014783025</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.81705219758317</v>
+        <v>12.94074881861142</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.58737753474594</v>
+        <v>13.73606708252377</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07379</t>
+          <t>X ≈ 0.07378</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>42</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.17979315831348</v>
+        <v>12.17963976830916</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12.31001830190177</v>
+        <v>12.30952380952377</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.222487657270307</v>
+        <v>7.270499336260627</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.32847609968677</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.2182463807703</v>
+        <v>16.29150349054999</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.60642282253562</v>
+        <v>10.70577014783019</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.81705219758317</v>
+        <v>12.94074881861142</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.39690134426976</v>
+        <v>12.54559089204759</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08008</t>
+          <t>X ≈ 0.08006</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.79025081757829</v>
+        <v>3.48246866571472</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.21900884458795</v>
+        <v>12.1796397683091</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.11393987052926</v>
+        <v>24.43073593073591</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.6932973762571</v>
+        <v>17.88088072917795</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.656387417637255</v>
+        <v>-0.02815193382129166</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.082431634861329</v>
+        <v>9.00210106786232</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.43889240283925</v>
+        <v>17.62717739838809</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>18.31908671690475</v>
+        <v>20.6205078195543</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.46916792057488</v>
+        <v>19.79667923873932</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.26446676231468</v>
+        <v>19.59253879120322</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.475315502905296</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.99634112018015</v>
+        <v>13.19494154139824</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.280900299818448</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1145 +2210,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.09912</t>
+          <t>X &gt; -0.09899</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02229869849929855</v>
+        <v>-0.03318127607688837</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.01369939654680508</v>
+        <v>-0.02479243202486714</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05433575871854401</v>
+        <v>-0.06525819087454465</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1300953805992009</v>
+        <v>-0.1165596250650935</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1678424012913524</v>
+        <v>-0.1550939912887443</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1008541636337057</v>
+        <v>-0.1121428274402092</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1235224191152255</v>
+        <v>-0.1352353311472356</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.007935821230766749</v>
+        <v>0.02031333080885389</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03357739122324688</v>
+        <v>0.04541381380336418</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.02660660719858754</v>
+        <v>0.01379318668802654</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.04239741820379095</v>
+        <v>-0.05500775507749722</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1407450291913577</v>
+        <v>-0.153619681162489</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1077489533492866</v>
+        <v>-0.1211221643391127</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.136825764966467</v>
+        <v>-0.1506690426425692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.09283</t>
+          <t>X &gt; -0.09271</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07554362516194146</v>
+        <v>-0.07465152288990851</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03738790767243216</v>
+        <v>-0.03725967739971736</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1013372268970727</v>
+        <v>-0.1010619860768358</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1288868789388573</v>
+        <v>-0.1285296472964035</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1161552241426307</v>
+        <v>-0.1169917055545611</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.07433650436238537</v>
+        <v>-0.07470377261893901</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09680102665524259</v>
+        <v>-0.09767720264765245</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.03656708915215034</v>
+        <v>0.03530354889041121</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.06249119883452181</v>
+        <v>0.06058945582920927</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.00926178484598239</v>
+        <v>0.006884784556291379</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.05931464743404291</v>
+        <v>-0.06152134137252574</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1825746854913106</v>
+        <v>-0.185014307151711</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1481460648481914</v>
+        <v>-0.151270949904621</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1535464823241242</v>
+        <v>-0.1572100221170487</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.08654</t>
+          <t>X &gt; -0.08642</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4063</v>
+        <v>4074</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05206421502895608</v>
+        <v>-0.05109543144435946</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.0307524303466451</v>
+        <v>-0.03063594871147046</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1422490606359901</v>
+        <v>-0.1418616596794493</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.04778511900006777</v>
+        <v>-0.04764236742689576</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.01665343773865402</v>
+        <v>0.01522935875068043</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.03274807443727212</v>
+        <v>0.03197901802938929</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01396957918696273</v>
+        <v>-0.01529662878066063</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.07307047809985079</v>
+        <v>0.07147329856632467</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1239915697013032</v>
+        <v>0.1215738859550086</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04991106120461808</v>
+        <v>0.04695046497916877</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.03116911467717642</v>
+        <v>0.02824240571479919</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1420059644270282</v>
+        <v>-0.1451430454943861</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1054421127981087</v>
+        <v>-0.1093901187616453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.111912892404078</v>
+        <v>-0.1165080849159352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.08025</t>
+          <t>X &gt; -0.08014</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4045</v>
+        <v>4056</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.007994762959981472</v>
+        <v>0.008934623871930114</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.08586188921916715</v>
+        <v>0.08566880873789273</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.04900368586801562</v>
+        <v>-0.048866091866266</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.003997316676070284</v>
+        <v>-0.003970205888563783</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06312818968754641</v>
+        <v>0.06135707939599655</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05331200617374066</v>
+        <v>0.05237777269265109</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0314473714619723</v>
+        <v>0.02977878025576075</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.17033126325137</v>
+        <v>0.1682453899730447</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1723910015815733</v>
+        <v>0.1695067972654201</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1264689244538246</v>
+        <v>0.1228473235280987</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.03446211223331375</v>
+        <v>0.03107044924708902</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01608698840998102</v>
+        <v>-0.02012799145219191</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02689170236065763</v>
+        <v>-0.0317299056330782</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.08382012481620649</v>
+        <v>-0.08927520677107736</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.07397</t>
+          <t>X &gt; -0.07386</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4028</v>
+        <v>4038</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.06814691397904227</v>
+        <v>-0.07861342942907612</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06631371798597741</v>
+        <v>0.05485923810530835</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.06746276311925214</v>
+        <v>-0.07853097343780746</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.04758447174851455</v>
+        <v>-0.05872388481084556</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04685053891427771</v>
+        <v>0.03376614373867426</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.06051341603617999</v>
+        <v>0.04824226021994349</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.06369849104616065</v>
+        <v>0.05053347599807267</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1803546793711135</v>
+        <v>0.1669669856554066</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1330917635055755</v>
+        <v>0.1189300832498859</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.09054980666264356</v>
+        <v>0.07571901802651126</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.05060612866259362</v>
+        <v>-0.06506171272243222</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1015345919713653</v>
+        <v>-0.1167712191066386</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.03617315135127086</v>
+        <v>-0.0524119139274859</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.09429684954778139</v>
+        <v>-0.1113290092569343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.06768</t>
+          <t>X &gt; -0.06758</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3990</v>
+        <v>4001</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.02026152141618809</v>
+        <v>-0.01883130670064048</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08081141963020144</v>
+        <v>0.08064580214256267</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1504576123272301</v>
+        <v>-0.1500378654562482</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.181648364764861</v>
+        <v>-0.1811269010221892</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1312469951298709</v>
+        <v>-0.1331750404888012</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.02027524390329916</v>
+        <v>-0.02134905847265856</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03376278027919</v>
+        <v>0.03140609417333451</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1559624140269378</v>
+        <v>0.1532113843671468</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.08379259925767713</v>
+        <v>0.08010630062059221</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02388234515291288</v>
+        <v>0.01912844995257501</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1166855483466236</v>
+        <v>-0.1210809224164819</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1934927017392809</v>
+        <v>-0.1988012807188539</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1485879113172146</v>
+        <v>-0.1552015688648183</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1342552360801506</v>
+        <v>-0.1170172850582176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06139</t>
+          <t>X &gt; -0.06129</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3965</v>
+        <v>3975</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02931934961909377</v>
+        <v>-0.02766448286091361</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.04280634895029323</v>
+        <v>-0.04262424989736502</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2227225649569888</v>
+        <v>-0.2220996529987929</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2549875695962669</v>
+        <v>-0.2542570353109923</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2259220608255674</v>
+        <v>-0.2279181025124473</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1161943011156907</v>
+        <v>-0.1171666098307114</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.01427573991708186</v>
+        <v>0.01164401110692381</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06476290217251091</v>
+        <v>0.06192426418241581</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.007503178312610714</v>
+        <v>-0.01143979731793365</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.0118567473568234</v>
+        <v>-0.01719207048257942</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1520133159782944</v>
+        <v>-0.1569927230341648</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1539153119622512</v>
+        <v>-0.160176741454201</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1059509946481541</v>
+        <v>-0.1136981756921855</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1072014730470912</v>
+        <v>-0.07688266462528048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.0551</t>
+          <t>X &gt; -0.05501</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3919</v>
+        <v>3926</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.0890585241730264</v>
+        <v>-0.06025145423453893</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1598038288666999</v>
+        <v>-0.1572807840905739</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.337179007334889</v>
+        <v>-0.3341185925409249</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3459531775990783</v>
+        <v>-0.3429152148664372</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2846475459807749</v>
+        <v>-0.2847655686157466</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1007486016012678</v>
+        <v>-0.09978848232618276</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.0186656848004958</v>
+        <v>-0.01946470427552782</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.03801372355720645</v>
+        <v>0.03723936084067248</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01659999044463945</v>
+        <v>-0.01114578080954942</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.0286192585660956</v>
+        <v>-0.05758863079572762</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.09147561463609577</v>
+        <v>-0.1202418531121552</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1703474063002304</v>
+        <v>-0.2005565833864438</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1567141310094087</v>
+        <v>-0.1740424158210203</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1861456152559526</v>
+        <v>-0.1398910877486585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04882</t>
+          <t>X &gt; -0.04873</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3852</v>
+        <v>3859</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.07283731484299949</v>
+        <v>-0.08242587447375627</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1164481479441974</v>
+        <v>-0.1279052882396812</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3936092596485565</v>
+        <v>-0.404339559856254</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3011935837335074</v>
+        <v>-0.3121699959384188</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3589088872747581</v>
+        <v>-0.3737963414246721</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2288835667320726</v>
+        <v>-0.2420833347193465</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1957597246700615</v>
+        <v>-0.2110861587755011</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1298876383600813</v>
+        <v>-0.1453734660127282</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1506467914441103</v>
+        <v>-0.1681238386425719</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.12980003411284</v>
+        <v>-0.1493510878242716</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2161391872302474</v>
+        <v>-0.2354667954766256</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2596426548126161</v>
+        <v>-0.2664143885517944</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2903854084375581</v>
+        <v>-0.2844115752605774</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2982946180241015</v>
+        <v>-0.2540198315192939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04253</t>
+          <t>X &gt; -0.04245</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3796</v>
+        <v>3804</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.0636800872868406</v>
+        <v>-0.06054410154404621</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.005374134110667228</v>
+        <v>-0.005238595577431227</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2281984294888701</v>
+        <v>-0.2275249324335604</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1625910415989367</v>
+        <v>-0.162072065323251</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.344701200343458</v>
+        <v>-0.3486212139353313</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2697554167705931</v>
+        <v>-0.2714029115948478</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2349058264390038</v>
+        <v>-0.2390906976012843</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1085426806966439</v>
+        <v>-0.1132186884647126</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.04971419998651072</v>
+        <v>-0.05699442791381415</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.0423349687030381</v>
+        <v>-0.05228307345828398</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1269049602415748</v>
+        <v>-0.136668172046285</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2505879248514731</v>
+        <v>-0.2477004970055319</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2228989467634079</v>
+        <v>-0.2076786154926111</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2605984914789161</v>
+        <v>-0.2067162062795447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03624</t>
+          <t>X &gt; -0.03616</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3695</v>
+        <v>3701</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.02988310553476481</v>
+        <v>0.02085209541458255</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.05318548104670384</v>
+        <v>0.04083444034768036</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1648853938205406</v>
+        <v>-0.176682070771335</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.209120669547346</v>
+        <v>-0.2207914693767563</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6516946746173105</v>
+        <v>-0.6684944239707917</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5288966808721298</v>
+        <v>-0.5159089866902562</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3285695422455603</v>
+        <v>-0.3192679622445738</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1588100267936525</v>
+        <v>-0.1500009129148694</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1237449612210639</v>
+        <v>-0.118179648760794</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.06966143327088048</v>
+        <v>0.07149214513118096</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.0538489266131208</v>
+        <v>-0.03652724715006173</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1277251720927026</v>
+        <v>-0.09822858709567583</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.08779483460774884</v>
+        <v>-0.04605840948826057</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1868223778859459</v>
+        <v>-0.105995992826557</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02995</t>
+          <t>X &gt; -0.02988</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3563</v>
+        <v>3568</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1146320764598627</v>
+        <v>-0.1038443374779163</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1145110871836152</v>
+        <v>-0.105043737918578</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.522177515077793</v>
+        <v>-0.5396584773049113</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5169622661101556</v>
+        <v>-0.5626875225027064</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.8999841752196787</v>
+        <v>-0.9119198614383848</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5313832937218237</v>
+        <v>-0.583127621812956</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3765238968605047</v>
+        <v>-0.4197568278124351</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1830129249484074</v>
+        <v>-0.2135089385178119</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2005018650899473</v>
+        <v>-0.2224781872513617</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.01196991766454403</v>
+        <v>-0.01018243314615574</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.04827365801848771</v>
+        <v>-0.01829935785950454</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1261604509339946</v>
+        <v>-0.08446126542219901</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.04111905052862852</v>
+        <v>0.012401656700888</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1241119997969093</v>
+        <v>-0.03101019938568328</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.02366</t>
+          <t>X &gt; -0.0236</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3389</v>
+        <v>3385</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.136474862737245</v>
+        <v>-0.07576541001533599</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2736795873162734</v>
+        <v>0.3045859423774644</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.01652827377074573</v>
+        <v>-0.0140419559306153</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.06334650580941315</v>
+        <v>-0.03178118014256626</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5721288296339324</v>
+        <v>-0.491505668009161</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3042620292700207</v>
+        <v>-0.2777694553608825</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.005378408010955127</v>
+        <v>0.01587029243756888</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1472047628969051</v>
+        <v>0.1405305937607579</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.17474429418764</v>
+        <v>0.1921319438799358</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2985640638064382</v>
+        <v>0.3426169148807219</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1823845933597568</v>
+        <v>0.2565750796859305</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1282410579015689</v>
+        <v>0.2261678577948416</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3572492485539343</v>
+        <v>0.4973811769743222</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2879126060687511</v>
+        <v>0.4678438851736004</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.01738</t>
+          <t>X &gt; -0.01732</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3582006887085569</v>
+        <v>0.3456786452928782</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6082133338150726</v>
+        <v>0.6415595748056475</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3711706556846366</v>
+        <v>0.4056498693192196</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4067585752982268</v>
+        <v>0.4092712842712842</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.005348012497776722</v>
+        <v>0.04628476958198036</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2920260171373101</v>
+        <v>0.3190702884009085</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5858645537702003</v>
+        <v>0.6056364213976835</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6235277711821965</v>
+        <v>0.6448541660648388</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7202743212840303</v>
+        <v>0.765709839756326</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7851820233768763</v>
+        <v>0.8888509559110318</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5804808651166837</v>
+        <v>0.6847105083749412</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6779505001218524</v>
+        <v>0.8060085588711488</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7625315080071786</v>
+        <v>0.9159011373578352</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6097182623346526</v>
+        <v>0.7861581205853199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.01109</t>
+          <t>X &gt; -0.01104</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7476456367017192</v>
+        <v>0.7366414218662598</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.981351924915657</v>
+        <v>0.9989872348648916</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9623919511616421</v>
+        <v>0.9811890961742478</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6484763362942445</v>
+        <v>0.666780587833216</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1101867831985501</v>
+        <v>0.1775314468812965</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2709021179241731</v>
+        <v>0.3136115658369292</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8694852332053244</v>
+        <v>0.9364824759279458</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.983216042783809</v>
+        <v>1.051647664963596</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.093057254897865</v>
+        <v>1.185556805655921</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.097255301752156</v>
+        <v>1.216136973986536</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8242247960372282</v>
+        <v>0.9436438265187945</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7561089272104553</v>
+        <v>0.8992815139862174</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8825928535348879</v>
+        <v>1.050945186875566</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8350111139425067</v>
+        <v>1.02657924916435</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0048</t>
+          <t>X &gt; -0.004753</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.080988731370411</v>
+        <v>1.074937755585935</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.298374066878011</v>
+        <v>1.284285460666545</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.360745539265828</v>
+        <v>1.310074550917825</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.110018301901803</v>
+        <v>1.058570338890704</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5336335107108781</v>
+        <v>0.5311823726146017</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.021483730822155</v>
+        <v>0.9946620180544343</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.470106704889318</v>
+        <v>1.506088308691666</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.574466632531148</v>
+        <v>1.574199102846841</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.513484476008372</v>
+        <v>1.537226493710044</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.46356567967851</v>
+        <v>1.514313244702848</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.296959759513555</v>
+        <v>1.348311622490939</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.25514743567841</v>
+        <v>1.330200709207475</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.139758487126905</v>
+        <v>1.240153385237086</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9845417564010575</v>
+        <v>1.107809994010658</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001488</t>
+          <t>X &gt; 0.001529</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.166090225050986</v>
+        <v>2.120760658334497</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.342214230289223</v>
+        <v>2.32729274543815</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.126173855364385</v>
+        <v>2.112525674349392</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.47981276124051</v>
+        <v>2.466123362096518</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.718109445857053</v>
+        <v>1.753160574612153</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.01548347549214</v>
+        <v>2.025946093431081</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.869110917834554</v>
+        <v>2.94963004894835</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.759504293708225</v>
+        <v>2.796996393710415</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.055984156845852</v>
+        <v>3.162708348332011</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.189085914582122</v>
+        <v>3.323219812259758</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.073750261237038</v>
+        <v>3.163822094030159</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.750666393931944</v>
+        <v>2.864046996943145</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.553929302906297</v>
+        <v>2.692602716911765</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.288154676099758</v>
+        <v>2.494220285862255</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.007776</t>
+          <t>X &gt; 0.007811</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.635967086348764</v>
+        <v>2.536714397797724</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.102703071207017</v>
+        <v>3.03470276529535</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.759879738400024</v>
+        <v>2.745023049613323</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.942052933936438</v>
+        <v>2.874907090828003</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.195971173048541</v>
+        <v>2.177541404610736</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.285552994891411</v>
+        <v>2.346268650796986</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.343699778482389</v>
+        <v>3.378224424214601</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.136371394435912</v>
+        <v>3.172537345412955</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.387077549601443</v>
+        <v>3.447739554174184</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.835860051972887</v>
+        <v>3.97666851758396</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.423366685920492</v>
+        <v>3.564411524782521</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.094108474639448</v>
+        <v>3.258374307933053</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.089542036910451</v>
+        <v>3.279449471899923</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.847745219604526</v>
+        <v>3.112261243384594</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.01406</t>
+          <t>X &gt; 0.01409</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1618</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.463459742024362</v>
+        <v>2.434263947671731</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.015438049454971</v>
+        <v>3.014251263010316</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.497057270385966</v>
+        <v>2.496903880381645</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.627282413974328</v>
+        <v>2.626787921596325</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.645235135291493</v>
+        <v>2.693781055057265</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.94260916492658</v>
+        <v>2.966566573876193</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.093992748800083</v>
+        <v>4.142004427790404</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.244971076583184</v>
+        <v>4.294218638976901</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.245793617217394</v>
+        <v>4.319050726997091</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.879187552655154</v>
+        <v>4.978534877949727</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.180048817139081</v>
+        <v>4.279956853157756</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.214426969494404</v>
+        <v>4.338123590522649</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.165104299122902</v>
+        <v>4.31379384690073</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.081816463564515</v>
+        <v>4.253815223131177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.02035</t>
+          <t>X &gt; 0.02038</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.050690976320176</v>
+        <v>1.917369091143549</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.038895591557946</v>
+        <v>2.013581318964796</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.17725444290344</v>
+        <v>2.306866231413451</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.764448360292263</v>
+        <v>2.81842966194111</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.530804656396867</v>
+        <v>2.558188154576975</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.599694299131734</v>
+        <v>2.601966039808119</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.733567336666781</v>
+        <v>3.839019874246773</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.799628928980574</v>
+        <v>3.9838741367642</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.195615546258253</v>
+        <v>4.404916794802972</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.792764533629843</v>
+        <v>5.031469893377306</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.435740450769494</v>
+        <v>4.674657690116028</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.393957140824746</v>
+        <v>4.656488549618324</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.887743835112254</v>
+        <v>5.177361157405635</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.732672173838402</v>
+        <v>5.04472663010803</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.02664</t>
+          <t>X &gt; 0.02666</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1013</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.70170983323662</v>
+        <v>2.672514038883989</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.163574085681191</v>
+        <v>3.162387299236535</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.953402898359514</v>
+        <v>3.953249508355192</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.169511556261796</v>
+        <v>5.169017063883793</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.236355270688307</v>
+        <v>4.284901190454079</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.731162666562291</v>
+        <v>4.755120075511904</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.929769187848933</v>
+        <v>5.977780866839254</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.660133910301091</v>
+        <v>5.709381472694808</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.092735169375558</v>
+        <v>6.165992279155255</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.42741657047906</v>
+        <v>6.526763895773634</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.222715412218868</v>
+        <v>6.322623448237543</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.454526930813088</v>
+        <v>6.578223551841333</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.712559690530284</v>
+        <v>7.861249238308112</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.148561875801235</v>
+        <v>7.320560635367897</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.03293</t>
+          <t>X &gt; 0.03294</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.815380265761945</v>
+        <v>3.855771982282363</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.796786765290712</v>
+        <v>4.744782783405867</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.389669701523324</v>
+        <v>5.339919949602908</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.137178795728971</v>
+        <v>6.087850962387421</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.858148501892536</v>
+        <v>4.856945455551696</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.785152161157242</v>
+        <v>4.758902791428717</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.058466493249107</v>
+        <v>6.057950039656909</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.579052170450019</v>
+        <v>6.580992433785305</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.147699643556876</v>
+        <v>6.173191641706602</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.902719118831953</v>
+        <v>6.956285186973211</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.821474750695216</v>
+        <v>6.87575413375108</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.596593643791287</v>
+        <v>7.675577236999786</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.904837852206271</v>
+        <v>9.010950830831511</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.513289551815511</v>
+        <v>8.641948721277039</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>662</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.618781854662025</v>
+        <v>4.589586060309394</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.877686396039273</v>
+        <v>5.876499609594617</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.936087216722306</v>
+        <v>5.935933826717985</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.576886378437557</v>
+        <v>7.576391886059554</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.528022807214974</v>
+        <v>5.576568726980746</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.919052425973931</v>
+        <v>4.943009834923544</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.042801281209279</v>
+        <v>6.0908129601996</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.482077048298663</v>
+        <v>6.53132461069238</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.118980088150515</v>
+        <v>6.192237197930211</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.779635309947537</v>
+        <v>6.87898263524211</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.028106357125417</v>
+        <v>7.128014393144092</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.119886322169556</v>
+        <v>8.243582943197801</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.11665389785917</v>
+        <v>10.26534344563699</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.284987735396889</v>
+        <v>9.456986494963552</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>529</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.473715349427842</v>
+        <v>3.44451955507521</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.319996175078572</v>
+        <v>4.318809388633916</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.24847620809291</v>
+        <v>5.248322818088589</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.970383771341005</v>
+        <v>8.969889278963002</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.163663216354941</v>
+        <v>6.212209136120713</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.461037245990028</v>
+        <v>6.484994654939641</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.943434637196454</v>
+        <v>6.991446316186774</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.988653328003295</v>
+        <v>8.037900890397012</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.171527504183722</v>
+        <v>7.244784613963418</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.022931959271645</v>
+        <v>8.122279284566218</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.007266717835648</v>
+        <v>8.107174753854324</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.230680787015167</v>
+        <v>8.354377408043412</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.322817268295324</v>
+        <v>9.471506816073152</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.603373334400878</v>
+        <v>8.77537209396754</v>
       </c>
     </row>
     <row r="30">
@@ -3465,306 +3465,306 @@
         <v>414</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.799277206180619</v>
+        <v>3.770081411827988</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.362004156595063</v>
+        <v>4.360817370150407</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.624237602757894</v>
+        <v>6.624084212753573</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.894559364703731</v>
+        <v>9.894064872325728</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.182356768129786</v>
+        <v>7.230902687895558</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.513547222885649</v>
+        <v>6.537504631835262</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.670382757339276</v>
+        <v>6.718394436329596</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.894135369591197</v>
+        <v>7.943382931984914</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.86696963818919</v>
+        <v>6.940226747968886</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.224780310458364</v>
+        <v>7.324127635752937</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.020079152198171</v>
+        <v>7.119987188216847</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.812911410833692</v>
+        <v>6.936608031861937</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.3589441323995</v>
+        <v>7.507633680177328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.135404420307196</v>
+        <v>6.307403179873859</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.05808</t>
+          <t>X &gt; 0.05807</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>324</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.926491376873052</v>
+        <v>4.897295582520421</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.698311676831963</v>
+        <v>5.698158286827642</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.371746696963534</v>
+        <v>7.371252204585531</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.290247267324631</v>
+        <v>5.338793187090403</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.576985011767619</v>
+        <v>4.624996690757939</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.961768219832742</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.209428038618597</v>
+        <v>6.282685148398294</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.211361094140599</v>
+        <v>7.310708419435173</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.006659935880407</v>
+        <v>7.106567971899082</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.115112162309799</v>
+        <v>6.238808783338044</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.312245259613675</v>
+        <v>6.460934807391503</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.068845107371075</v>
+        <v>4.240843866937738</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.06437</t>
+          <t>X &gt; 0.06435</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>244</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.666624953072208</v>
+        <v>3.637429158719577</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.05543886000838</v>
+        <v>2.054252073563724</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.660667475253341</v>
+        <v>1.660514085249019</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.659745077858091</v>
+        <v>4.659250585480088</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.02309486902469615</v>
+        <v>0.07164078879046798</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9090392980615292</v>
+        <v>-0.8850818891119161</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.6455946049673855</v>
+        <v>0.6936062839577062</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.457214485770812</v>
+        <v>3.506462048164529</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.8060683948218</v>
+        <v>3.879325504601496</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.595493860787023</v>
+        <v>4.694841186081597</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.210464833674372</v>
+        <v>5.310372869693047</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.425170854882154</v>
+        <v>4.548867475910399</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.005020001568745</v>
+        <v>4.153709549346573</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.9520671272051118</v>
+        <v>1.124065886771774</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07065</t>
+          <t>X &gt; 0.07063</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>160</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.769083969465647</v>
+        <v>3.739888175113016</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9671021235981812</v>
+        <v>-0.9682889100428369</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.513126491646787</v>
+        <v>0.5129731016424657</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.143351635235135</v>
+        <v>3.142857142857132</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.394937917860553</v>
+        <v>-2.346391998094781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.972563888225466</v>
+        <v>-3.948606479275853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.807274247491627</v>
+        <v>-2.759262568501306</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4756571087216273</v>
+        <v>0.524904671115344</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.914674952198858</v>
+        <v>2.987932061978555</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.439756155868984</v>
+        <v>1.539103481163558</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.485054997608799</v>
+        <v>2.584963033627474</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.025717703349287</v>
+        <v>-0.877028155571459</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.674982053122754</v>
+        <v>-2.502983293556092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.07694</t>
+          <t>X &gt; 0.07692</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>118</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.06145685082158536</v>
+        <v>0.03226105646895405</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.787017377835468</v>
+        <v>-5.788204164280124</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.639415881234576</v>
+        <v>-3.639569271238898</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1193602291716402</v>
+        <v>-0.1198547215496433</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-5.742395544979196</v>
+        <v>-5.693849625213424</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.682309650937327</v>
+        <v>-9.658352241987714</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.377189501728921</v>
+        <v>-6.3291778227386</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.820494539326567</v>
+        <v>-1.747237429546871</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.822955708537791</v>
+        <v>-1.723608383243217</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.362173641676598</v>
+        <v>1.462081677695274</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.535651595798591</v>
+        <v>-4.411954974770346</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.803260076230643</v>
+        <v>-5.654570528452815</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.272439680241398</v>
+        <v>-7.100440920674735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08323</t>
+          <t>X &gt; 0.0832</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.7454059425340347</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-8.85400688550294</v>
+        <v>-9.387406557101656</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-9.248778270257979</v>
+        <v>-9.78114454541636</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-9.118553126669617</v>
+        <v>-9.65126050420168</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-14.41874744167008</v>
+        <v>-14.84639199809478</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-12.93089722155879</v>
+        <v>-13.39713589104056</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-11.82513139034878</v>
+        <v>-12.28132139203073</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-13.4826762246117</v>
+        <v>-13.92362474064937</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.972229809705908</v>
+        <v>-10.43118558508027</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.631672415559578</v>
+        <v>-10.07854357765996</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.074468811915011</v>
+        <v>-5.576801672254881</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.801995421464447</v>
+        <v>-10.22451728783116</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-12.60309865573024</v>
+        <v>-12.97261639086557</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-13.5678391959799</v>
+        <v>-13.9000421170855</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1145 +3904,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.09912</t>
+          <t>X &lt; -0.09899</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.607535233936545</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>1.200828737015989</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>3.160031925171864</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>7.506549178375806</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.032011466794074</v>
+        <v>6.542208019733984</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3874381293736064</v>
+        <v>-0.982448270061127</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-2.195891467433214</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.298339082226242</v>
+        <v>-0.6667788717776091</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>7.422541535698244</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.850913020899128</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.670256042115341</v>
+        <v>7.276428471149785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.09283</t>
+          <t>X &lt; -0.09271</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.189187062249154</v>
+        <v>3.159991267896523</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.578000969185325</v>
+        <v>1.576814182740669</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.276013089584929</v>
+        <v>4.275859699580607</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.437166068224833</v>
+        <v>5.43667157584683</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.898876515129139</v>
+        <v>4.947422434894911</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.134394874661126</v>
+        <v>3.158352283610739</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.080612350446515</v>
+        <v>4.128624029436835</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.541095468597959</v>
+        <v>-1.491847906204242</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.633005460172278</v>
+        <v>-2.559748350392582</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.3901407513475021</v>
+        <v>-0.2907934260529288</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.497941595546948</v>
+        <v>2.597849631565623</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.686958923159992</v>
+        <v>7.810655544188236</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.23588023479504</v>
+        <v>6.384569782572868</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.461615885021573</v>
+        <v>6.633614644588235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.08654</t>
+          <t>X &lt; -0.08642</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>116</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.829428797051854</v>
+        <v>1.800233002699223</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.080311669505264</v>
+        <v>1.079124883060608</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.995885112336438</v>
+        <v>4.995731722332117</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.677834393855825</v>
+        <v>1.677339901477822</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5845930902743461</v>
+        <v>-0.5360471705085743</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.149288026156505</v>
+        <v>-1.125330617206892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.5381512246021316</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.56313599472665</v>
+        <v>-2.513888432332934</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.34825608228391</v>
+        <v>-4.274998972504214</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.749899016544802</v>
+        <v>-1.650551691250229</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.092531209287756</v>
+        <v>-0.9926231732690809</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.976329701688258</v>
+        <v>5.100026322716502</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.69410988285761</v>
+        <v>3.842799430635438</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.919845533084143</v>
+        <v>4.091844292650805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.08025</t>
+          <t>X &lt; -0.08014</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>134</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2421100603851016</v>
+        <v>-0.2713058547377329</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.59956481016534</v>
+        <v>-2.600751596609996</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.483275745378116</v>
+        <v>1.483122355373794</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1209635755336507</v>
+        <v>0.1204690831556476</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.909863290994885</v>
+        <v>-1.861317371229113</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.612489261359798</v>
+        <v>-1.588531852410185</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.950930963909542</v>
+        <v>-0.9029192849192214</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.821437873981758</v>
+        <v>-3.722090548687184</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.041064405376275</v>
+        <v>-0.9411563693575999</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.485851060411882</v>
+        <v>0.6095476814401266</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8119688638148901</v>
+        <v>0.9606584115927177</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.530241827474264</v>
+        <v>2.702240587040926</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.07397</t>
+          <t>X &lt; -0.07386</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.82371973105505</v>
+        <v>2.095151333007749</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.774221328896196</v>
+        <v>-1.461709962674419</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.8045172201236</v>
+        <v>2.091920470063506</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.27249070808282</v>
+        <v>1.563909774436091</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.252553811900292</v>
+        <v>-0.8990235770421506</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.617431437894339</v>
+        <v>-1.284132795065318</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.702141797160508</v>
+        <v>-1.344788884290779</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.818217063463798</v>
+        <v>-4.442200592042553</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.554695908728306</v>
+        <v>-3.163383727495138</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.417859738170748</v>
+        <v>-2.013528097783805</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.350949037343895</v>
+        <v>1.729699875732742</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.709830500957501</v>
+        <v>3.103656086781832</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.9651763363858095</v>
+        <v>1.392708686533808</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.515415297870625</v>
+        <v>2.957543022233374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.06768</t>
+          <t>X &lt; -0.06758</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>189</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.429136879518552</v>
+        <v>0.3999410851659206</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.185084163604451</v>
+        <v>3.184930773600129</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.844409836293337</v>
+        <v>3.843915343915334</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.777019754097118</v>
+        <v>2.82556567386289</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4288911382295595</v>
+        <v>0.4528485471791726</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7140202792376655</v>
+        <v>-0.6660086002473449</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.297491039426525</v>
+        <v>-3.248243477032808</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.771171608647705</v>
+        <v>-1.697914498868009</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.465213727767534</v>
+        <v>2.565121763786209</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.086893467424439</v>
+        <v>4.210590088452683</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.137642085010505</v>
+        <v>3.286331632788333</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.834277206136498</v>
+        <v>2.477175436602643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06139</t>
+          <t>X &lt; -0.06129</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5423397834191306</v>
+        <v>0.5131439890664993</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7916188066343821</v>
+        <v>0.7904320201897264</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.117777654437482</v>
+        <v>4.117624264433161</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.713119077095605</v>
+        <v>4.712624584717602</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.174829523999911</v>
+        <v>4.223375443765683</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.146622158286156</v>
+        <v>2.17057956723577</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2636695963288389</v>
+        <v>-0.2156579173385182</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.195854519185346</v>
+        <v>-1.146606956791629</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1385121615011755</v>
+        <v>0.2117692712808719</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2188259233108525</v>
+        <v>0.3181732486054258</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.804822439469262</v>
+        <v>2.904730475487938</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.839200591824586</v>
+        <v>2.96289721285283</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.953933459441416</v>
+        <v>2.102623007219243</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.986232900148273</v>
+        <v>1.421435311095074</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.0551</t>
+          <t>X &lt; -0.05501</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.335877862595417</v>
+        <v>0.8989790842039227</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.396447494722437</v>
+        <v>2.346105029351108</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.055111224471204</v>
+        <v>4.982670071339427</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.185336368059566</v>
+        <v>5.112554112554108</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.265367425650901</v>
+        <v>4.244517092814313</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.509306340782167</v>
+        <v>1.486999581330203</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2795578135770711</v>
+        <v>0.2899798557411088</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5691902195226533</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2484929867324439</v>
+        <v>0.1659623650088449</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4283057741896101</v>
+        <v>0.857285299345385</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.368642783868346</v>
+        <v>1.789508488172935</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.548059104162597</v>
+        <v>2.98403886190146</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.353113714275231</v>
+        <v>2.588880935337635</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.805787177646479</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04882</t>
+          <t>X &lt; -0.04873</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.9642084168048584</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.362443330947272</v>
+        <v>1.495834957026652</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.604035582555873</v>
+        <v>4.727474612216469</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.522139514023017</v>
+        <v>3.648899438929654</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.195971173048541</v>
+        <v>4.368109512479229</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.675163384501808</v>
+        <v>2.828206209545897</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.287422722205335</v>
+        <v>2.465435316695064</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.517323775388292</v>
+        <v>1.697487752686342</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.75937192189582</v>
+        <v>1.962629947174925</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.515513731626569</v>
+        <v>1.743030973610693</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.522933785487588</v>
+        <v>2.747349740576112</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.039949867289351</v>
+        <v>3.107631281566377</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.410257906406812</v>
+        <v>3.316702962253316</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.513855867366544</v>
+        <v>2.961518217017918</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04253</t>
+          <t>X &lt; -0.04245</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6278922596210847</v>
+        <v>0.5986964652684534</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.05297559660907325</v>
+        <v>0.0517888101644175</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.24887778698357</v>
+        <v>2.248724396979249</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.601900858033069</v>
+        <v>1.601406365655066</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.395217522553949</v>
+        <v>3.443763442319721</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.656322122137233</v>
+        <v>2.680279531086846</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.312544405358111</v>
+        <v>2.360556084348431</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.068273689032509</v>
+        <v>1.117521251426226</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4891568174838241</v>
+        <v>0.5624139272635205</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4164400936928274</v>
+        <v>0.5157874189874008</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.248008365484452</v>
+        <v>1.347916401503127</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.470731851262819</v>
+        <v>2.442352568919823</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.203448963317378</v>
+        <v>2.047194642355997</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.582850845049563</v>
+        <v>2.03717214685841</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03624</t>
+          <t>X &lt; -0.03616</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2268176698786064</v>
+        <v>-0.1583735835781823</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4035775334342446</v>
+        <v>-0.3100578261982534</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.250831409679563</v>
+        <v>1.341193960538163</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.585974586054817</v>
+        <v>1.675576979257954</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.941127655909938</v>
+        <v>5.071808410903174</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.00899348882372</v>
+        <v>3.91310108718632</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.489856900049347</v>
+        <v>2.42095215542507</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.203116125115066</v>
+        <v>1.137123485021277</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.937215935805412</v>
+        <v>0.8956518983793629</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5274569588851108</v>
+        <v>-0.5416736149509589</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4085662912432895</v>
+        <v>0.2766808250385111</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.971079240499094</v>
+        <v>0.7438455174136323</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6688699255166881</v>
+        <v>0.3486875908498064</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.426257616298727</v>
+        <v>0.8022314303702913</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02995</t>
+          <t>X &lt; -0.02988</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6591805878231369</v>
+        <v>0.5900471576249444</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6583004528913534</v>
+        <v>0.596695191705976</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.001049196960793</v>
+        <v>3.064642418017655</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.970243744735946</v>
+        <v>3.194526459232335</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.16947432046473</v>
+        <v>5.185455135663183</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.051389412901749</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.161526074569558</v>
+        <v>2.39449142510891</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.050335047530005</v>
+        <v>1.219904671115344</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.150383486820424</v>
+        <v>1.273188472234956</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.06878841393350399</v>
+        <v>0.05836511840273317</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2778659830692192</v>
+        <v>0.1050594966499858</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7273619525531174</v>
+        <v>0.4847696423750065</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.2374508541871805</v>
+        <v>-0.07115998836888338</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.1778848736464838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.02366</t>
+          <t>X &lt; -0.0236</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5777606236479187</v>
+        <v>0.3154410006658424</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.158269414484579</v>
+        <v>-1.267736084490011</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.06993048665302126</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2683516352351418</v>
+        <v>0.1324020383060898</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.4267141472208</v>
+        <v>2.050159726043155</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.292160422551476</v>
+        <v>1.160055666223535</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.02287004359995848</v>
+        <v>-0.06636133393340771</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6267298259517418</v>
+        <v>-0.5883524364248345</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7449162427697047</v>
+        <v>-0.8053847697046166</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.274349637581885</v>
+        <v>-1.437972107436181</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7794468939422714</v>
+        <v>-1.078188331136793</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5487486682176979</v>
+        <v>-0.9515907259020437</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.530616565549039</v>
+        <v>-2.092090267372704</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.235108635401232</v>
+        <v>-1.967269007841807</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.01738</t>
+          <t>X &lt; -0.01732</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.111053016835719</v>
+        <v>-1.059434842295104</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.888380282266155</v>
+        <v>-1.965629335574747</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.244045291387557</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.265382417757984</v>
+        <v>-1.256367663344406</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.01665343773865402</v>
+        <v>-0.1422212900443469</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9102482540071719</v>
+        <v>-0.9813734695671172</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.827943538830219</v>
+        <v>-1.864583268209763</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.947372447928615</v>
+        <v>-1.987254861958583</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.251745166144339</v>
+        <v>-2.361994909783867</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.457084910271192</v>
+        <v>-2.744522249830581</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.81830468618567</v>
+        <v>-2.116256478567642</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.12572016358682</v>
+        <v>-2.493588979007633</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.393291960775024</v>
+        <v>-2.836339006011343</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.91556679048648</v>
+        <v>-2.436936326824188</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.01109</t>
+          <t>X &lt; -0.01104</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.729927888241868</v>
+        <v>-1.687872200767956</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.272481870433623</v>
+        <v>-2.290781073052237</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.230341441844907</v>
+        <v>-2.251732780710483</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.504033467775955</v>
+        <v>-1.531397174254323</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2557626601285961</v>
+        <v>-0.4080573555181886</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6293099199714973</v>
+        <v>-0.7214052214142228</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.021432309445565</v>
+        <v>-2.155899075188962</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.287657676651989</v>
+        <v>-2.422929974553945</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.545249471031056</v>
+        <v>-2.733600640937134</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.557059130755214</v>
+        <v>-2.80632238634432</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.922315520319486</v>
+        <v>-2.179243754059975</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.764857121168248</v>
+        <v>-2.078434210050283</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.06173127078744</v>
+        <v>-2.43088191051217</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.952138602643515</v>
+        <v>-2.376401015075082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0048</t>
+          <t>X &lt; -0.004753</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.810845832704096</v>
+        <v>-1.782724095601715</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.176393311337641</v>
+        <v>-2.131263593587143</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.282400664902745</v>
+        <v>-2.175437284677997</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.863042226657441</v>
+        <v>-1.75891725511498</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8962175083915795</v>
+        <v>-0.8831706918170354</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.716641993219064</v>
+        <v>-1.65482475338753</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.472152530643456</v>
+        <v>-2.507278441517194</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.649342891278373</v>
+        <v>-2.62233166941833</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.548362251136616</v>
+        <v>-2.562369908777967</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.465892111139986</v>
+        <v>-2.525782015019644</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.186589189931347</v>
+        <v>-2.250332956187926</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.117456310190121</v>
+        <v>-2.221519910536294</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.924029600455391</v>
+        <v>-2.072455179153351</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.663077291217988</v>
+        <v>-1.852473089474458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001488</t>
+          <t>X &lt; 0.001529</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1941</v>
+        <v>1955</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.408485808626828</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.684012005830645</v>
+        <v>-2.64438194512163</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.437693180484374</v>
+        <v>-2.401574202528451</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.844603259690537</v>
+        <v>-2.804980007270089</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.971860994783626</v>
+        <v>-1.99506816917421</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.314341723012539</v>
+        <v>-2.306668119622259</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.296237286506006</v>
+        <v>-3.360052578694997</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.171941761334871</v>
+        <v>-3.187805680745946</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.514538819640812</v>
+        <v>-3.6064556931235</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.669498342845657</v>
+        <v>-3.791422297294837</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.538607553831532</v>
+        <v>-3.611410817240753</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.168292017302988</v>
+        <v>-3.27089680029021</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.943199680692231</v>
+        <v>-3.07667028236083</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.638274170587977</v>
+        <v>-2.851448766701871</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.007776</t>
+          <t>X &lt; 0.007811</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2254</v>
+        <v>2268</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.238304649855039</v>
+        <v>-2.137468247508643</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.635791443986534</v>
+        <v>-2.55820119074459</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.345593155152336</v>
+        <v>-2.315021632890229</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.501524689853198</v>
+        <v>-2.425623980935669</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.867982548881322</v>
+        <v>-1.838047685402643</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.945043994326255</v>
+        <v>-1.981339343950722</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.846803216974166</v>
+        <v>-2.854042788281532</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.671466785083688</v>
+        <v>-2.681449770397414</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.886287863206199</v>
+        <v>-2.91533454602849</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.270164127567675</v>
+        <v>-3.364065532920947</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.919796575275562</v>
+        <v>-3.016644187860862</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.640141318120982</v>
+        <v>-2.758852607862259</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.637413933947954</v>
+        <v>-2.777920619211827</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.432080544693299</v>
+        <v>-2.637463011369142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.01406</t>
+          <t>X &lt; 0.01409</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2561</v>
+        <v>2572</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.548515098133421</v>
+        <v>-1.52365147672451</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.896221828223126</v>
+        <v>-1.887406557101656</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.570854845833786</v>
+        <v>-1.564069097350966</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.653420048934436</v>
+        <v>-1.64606617240235</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.665365933424752</v>
+        <v>-1.688701180582186</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.85330542189616</v>
+        <v>-1.860428184702201</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.579470509173873</v>
+        <v>-2.598589827128684</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.675638177604817</v>
+        <v>-2.69513023966821</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.677199560661627</v>
+        <v>-2.71176720073003</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.077787703780132</v>
+        <v>-3.127045587159415</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.637799916587774</v>
+        <v>-2.689308811032717</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.660531734936384</v>
+        <v>-2.726916849054248</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.630421060101817</v>
+        <v>-2.712677203375577</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.578828206968907</v>
+        <v>-2.676000400865576</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.02035</t>
+          <t>X &lt; 0.02038</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2866</v>
+        <v>2880</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9352404487351222</v>
+        <v>-0.8682175974414221</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9301841249880383</v>
+        <v>-0.9120994217994038</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9936514019924232</v>
+        <v>-1.045311229038965</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.262072565043027</v>
+        <v>-1.277558082056352</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.155807483077943</v>
+        <v>-1.159995321043894</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.187682190243557</v>
+        <v>-1.180254678721838</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.70629095476626</v>
+        <v>-1.741986849762135</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.737086623868898</v>
+        <v>-1.808342037131361</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.918788997644405</v>
+        <v>-2.000152860031854</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.192648025315677</v>
+        <v>-2.285445756007036</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.030019941394336</v>
+        <v>-2.124107379137008</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.011598928139087</v>
+        <v>-2.116585704371964</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.238440061214654</v>
+        <v>-2.354162831031367</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.168178145237199</v>
+        <v>-2.294649960222763</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.02664</t>
+          <t>X &lt; 0.02666</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3166</v>
+        <v>3177</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8609097392477807</v>
+        <v>-0.8486698186173882</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.008401683069543</v>
+        <v>-1.004546357518535</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.260559375523506</v>
+        <v>-1.25616115180798</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.648839800533118</v>
+        <v>-1.642991617732761</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.351630831246375</v>
+        <v>-1.362399531051466</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.509977246763583</v>
+        <v>-1.512381989479934</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.893115722436477</v>
+        <v>-1.901850508199807</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.80760266429224</v>
+        <v>-1.81702903922082</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.946370459343257</v>
+        <v>-1.962963601126418</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.053934695866019</v>
+        <v>-2.078469609059631</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.98914822107217</v>
+        <v>-2.014093570146109</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.063900183369213</v>
+        <v>-2.096175041841853</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.466947573889236</v>
+        <v>-2.505804115294552</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.287268850343217</v>
+        <v>-2.334191980997069</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.03293</t>
+          <t>X &lt; 0.03294</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3369</v>
+        <v>3381</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9137959832250644</v>
+        <v>-0.9190688077980056</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.149185826644612</v>
+        <v>-1.131308361855389</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.291607236163877</v>
+        <v>-1.273583502131132</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.471179291074421</v>
+        <v>-1.452394995155252</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.164920155871208</v>
+        <v>-1.159076363876487</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.147756366756703</v>
+        <v>-1.136014269184386</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.453601261709643</v>
+        <v>-1.446541198961761</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.578972520908003</v>
+        <v>-1.571899285188174</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.475885213776252</v>
+        <v>-1.474929721837164</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.657634890677109</v>
+        <v>-1.662521334198317</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.638610482818251</v>
+        <v>-1.643760370627845</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.825345847366044</v>
+        <v>-1.835513445088033</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.140331946672724</v>
+        <v>-2.155487646996654</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.046828298299367</v>
+        <v>-2.067830971757814</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3517</v>
+        <v>3528</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.8661851523473842</v>
+        <v>-0.8580361400521852</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.102586680129775</v>
+        <v>-1.098938627556954</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.113857635337347</v>
+        <v>-1.110366824890455</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.42214311951394</v>
+        <v>-1.4176290075103</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.037876091428338</v>
+        <v>-1.043734378643272</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.9238050229772412</v>
+        <v>-0.9254164340269853</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.135168685630113</v>
+        <v>-1.140627490707821</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.218034347423703</v>
+        <v>-1.223468277384939</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.150131975683038</v>
+        <v>-1.160277674789079</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.274671563528905</v>
+        <v>-1.289322339900991</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.321763184209381</v>
+        <v>-1.336376530235462</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.527526213491406</v>
+        <v>-1.5459637134269</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.90370235371882</v>
+        <v>-1.925660912726457</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.74770027888335</v>
+        <v>-1.774525243669466</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3650</v>
+        <v>3661</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5016640512823685</v>
+        <v>-0.4959583137274848</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6240518778308441</v>
+        <v>-0.6220120246630358</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7583840246056113</v>
+        <v>-0.7560900791854266</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.296539075147372</v>
+        <v>-1.292582791765575</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8911117358436087</v>
+        <v>-0.8954383196206663</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9343599516481049</v>
+        <v>-0.9350128570354599</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.004396205380615</v>
+        <v>-1.008308370028033</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.155907442700695</v>
+        <v>-1.15954446987184</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.037958426734114</v>
+        <v>-1.045414910198211</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.161502738493347</v>
+        <v>-1.172356273270267</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.159552174578444</v>
+        <v>-1.170495481656374</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.192231691218794</v>
+        <v>-1.206515328652735</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.350799872617984</v>
+        <v>-1.368221492545793</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.246899861341937</v>
+        <v>-1.268006511256168</v>
       </c>
     </row>
     <row r="30">
@@ -5156,309 +5156,309 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3765</v>
+        <v>3776</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.416331594324717</v>
+        <v>-0.4119328858529414</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4781227749087478</v>
+        <v>-0.4766046439393463</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7262802880142374</v>
+        <v>-0.724153911824672</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.085125185956912</v>
+        <v>-1.081918345785226</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.787889693165269</v>
+        <v>-0.7909098316482783</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7147120461899448</v>
+        <v>-0.7152555279016397</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7321151806835786</v>
+        <v>-0.7352406282422592</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.8666592529861461</v>
+        <v>-0.8695294907037976</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7540916260504815</v>
+        <v>-0.7599190356146863</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7935948656221186</v>
+        <v>-0.8021663601062698</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7713144291427909</v>
+        <v>-0.7800144736495795</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7487510815198135</v>
+        <v>-0.7601259198493509</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8089758021278328</v>
+        <v>-0.8229177504880596</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6746500478106654</v>
+        <v>-0.691542615589988</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.05808</t>
+          <t>X &lt; 0.05807</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3855</v>
+        <v>3866</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4126637037504821</v>
+        <v>-0.4090548514402172</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3553552914285447</v>
+        <v>-0.3542481673919937</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4775615580169514</v>
+        <v>-0.4761937799670335</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6179678990468744</v>
+        <v>-0.6161727849034335</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4435921621669721</v>
+        <v>-0.446391998094775</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3133288377465675</v>
+        <v>-0.3144428241390429</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3839832065801971</v>
+        <v>-0.3869090957411814</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5002882422237249</v>
+        <v>-0.5029878908681198</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5212058768166941</v>
+        <v>-0.5258563647845591</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.605462812775734</v>
+        <v>-0.6120593095341107</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5884286726866961</v>
+        <v>-0.5951222597299832</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5136884471320613</v>
+        <v>-0.5225889466911937</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5303857531418146</v>
+        <v>-0.5413351118683352</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3419729740047259</v>
+        <v>-0.3554147472550042</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.06437</t>
+          <t>X &lt; 0.06435</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3935</v>
+        <v>3946</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.226610052824114</v>
+        <v>-0.2241810342832977</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1270653868360867</v>
+        <v>-0.1266390868998357</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1026869903603185</v>
+        <v>-0.1023920739956523</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.288207300126075</v>
+        <v>-0.2873754152823977</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.001428790071507535</v>
+        <v>-0.004419810989851669</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05625300246689591</v>
+        <v>0.05461810342520579</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.03996070106849459</v>
+        <v>-0.04281303650029855</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2140472810271703</v>
+        <v>-0.2164920900182565</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2357057584610516</v>
+        <v>-0.2395736327822746</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2846662863752343</v>
+        <v>-0.2900104428870662</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3228424122439222</v>
+        <v>-0.3281162269448288</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2742549374120529</v>
+        <v>-0.2811356798688252</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2482786789590463</v>
+        <v>-0.2567785989461697</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.05903542034003806</v>
+        <v>-0.06950635488401957</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07065</t>
+          <t>X &lt; 0.07063</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4019</v>
+        <v>4030</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1495668241851433</v>
+        <v>-0.1480044788568122</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.03838658888011537</v>
+        <v>0.03832910084285857</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.02037226765843059</v>
+        <v>-0.02031073899104996</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1248290547623725</v>
+        <v>-0.1244695898161226</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.09513159554560957</v>
+        <v>0.09294942304907039</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1578371547345512</v>
+        <v>0.156457909035197</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1115657922500475</v>
+        <v>0.1093589326133753</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.0189081086696774</v>
+        <v>-0.02080890668445079</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1158916481987688</v>
+        <v>-0.1184805774266593</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05726099551057473</v>
+        <v>-0.06104525458259502</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.09885847827384708</v>
+        <v>-0.1025524635210502</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0007732663502295622</v>
+        <v>-0.005679752817158601</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.04082458520792898</v>
+        <v>0.03481133835065009</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1064934382930218</v>
+        <v>0.09937402654316685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.07694</t>
+          <t>X &lt; 0.07692</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4061</v>
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.001780046243723632</v>
+        <v>-0.0009318983263923997</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1676572675140235</v>
+        <v>0.1672399831990816</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1054644091320469</v>
+        <v>0.105184710753413</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.003459716787588718</v>
+        <v>0.003464688178056008</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1664871435645097</v>
+        <v>0.1646347110451387</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2807846003466636</v>
+        <v>0.2793346971947415</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1849823896765059</v>
+        <v>0.1830946268897122</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1494031131474998</v>
+        <v>0.1475750977950838</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.05283284693570067</v>
+        <v>0.05057003107347668</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.05291728748030522</v>
+        <v>0.04989837812136955</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.03955130160380804</v>
+        <v>-0.04233757986945363</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1317270214876274</v>
+        <v>0.1277885829707657</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1685831336768118</v>
+        <v>0.1638201135176658</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2113144255770791</v>
+        <v>0.2057593390568755</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08323</t>
+          <t>X &lt; 0.0832</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.002044047362439017</v>
+        <v>0.01538598958605775</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1810899874317613</v>
+        <v>0.1938133488835661</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1892102714811656</v>
+        <v>0.2019915661711309</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1865915865140764</v>
+        <v>0.199357750390547</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2951205616716166</v>
+        <v>0.3067436363242777</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2647319928371701</v>
+        <v>0.2768676272157578</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2421528612358159</v>
+        <v>0.253869727218536</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2761630828742696</v>
+        <v>0.2878881301277474</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2043090985403211</v>
+        <v>0.2157301155065312</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1973799665545215</v>
+        <v>0.2084877595768049</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1040154661300363</v>
+        <v>0.1153914659546444</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2009684196736643</v>
+        <v>0.211610413797338</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2584619841507134</v>
+        <v>0.2685514839804171</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2783146501739466</v>
+        <v>0.2878206041296636</v>
       </c>
     </row>
   </sheetData>
